--- a/resources/Variables_Notes.xlsx
+++ b/resources/Variables_Notes.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10404"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/k2474440/PycharmProjects/Data_Monitoring/resources/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{175C30AF-946A-7845-92EB-4B584A9529D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82F8E4B2-9561-BF47-A21B-E7B212C760EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="22100" windowWidth="24280" windowHeight="17500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="22200" windowWidth="24260" windowHeight="17400" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="P1" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3275" uniqueCount="1360">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3290" uniqueCount="1368">
   <si>
     <t>Page in CRF</t>
   </si>
@@ -4293,12 +4293,36 @@
   <si>
     <t>....Treat</t>
   </si>
+  <si>
+    <t>No topical therapy to date</t>
+  </si>
+  <si>
+    <t>noTopT</t>
+  </si>
+  <si>
+    <t>Integer</t>
+  </si>
+  <si>
+    <t>1 = Yes</t>
+  </si>
+  <si>
+    <t>noCurrSyst</t>
+  </si>
+  <si>
+    <t>No current systemic therapy (AD or Other)</t>
+  </si>
+  <si>
+    <t>noCurTop</t>
+  </si>
+  <si>
+    <t>No current local/UV therapy</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="21" x14ac:knownFonts="1">
+  <fonts count="22" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4431,6 +4455,13 @@
       <color theme="1"/>
       <name val="Calibri (Body)"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -4459,7 +4490,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
@@ -4548,6 +4579,14 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="16" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -7969,7 +8008,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AV496"/>
+  <dimension ref="A1:AV499"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="31.1640625" style="11" customWidth="1"/>
@@ -12697,38 +12736,38 @@
       <c r="F215" s="12"/>
       <c r="G215" s="12"/>
     </row>
-    <row r="216" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A216" s="11" t="s">
-        <v>461</v>
+    <row r="216" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A216" s="43" t="s">
+        <v>1361</v>
       </c>
       <c r="B216" s="11">
         <v>4</v>
       </c>
-      <c r="C216" s="12" t="s">
-        <v>460</v>
-      </c>
-      <c r="D216" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="E216" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="F216" s="12">
-        <v>1</v>
-      </c>
-      <c r="G216" s="12" t="s">
-        <v>58</v>
+      <c r="C216" s="42" t="s">
+        <v>1360</v>
+      </c>
+      <c r="D216" s="44" t="s">
+        <v>6</v>
+      </c>
+      <c r="E216" s="44" t="s">
+        <v>1362</v>
+      </c>
+      <c r="F216" s="42">
+        <v>1</v>
+      </c>
+      <c r="G216" s="42" t="s">
+        <v>1363</v>
       </c>
     </row>
     <row r="217" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A217" s="11" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="B217" s="11">
         <v>4</v>
       </c>
       <c r="C217" s="12" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="D217" s="12" t="s">
         <v>6</v>
@@ -12745,13 +12784,13 @@
     </row>
     <row r="218" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A218" s="11" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="B218" s="11">
         <v>4</v>
       </c>
       <c r="C218" s="12" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="D218" s="12" t="s">
         <v>6</v>
@@ -12768,13 +12807,13 @@
     </row>
     <row r="219" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A219" s="11" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="B219" s="11">
         <v>4</v>
       </c>
       <c r="C219" s="12" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="D219" s="12" t="s">
         <v>6</v>
@@ -12791,13 +12830,13 @@
     </row>
     <row r="220" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A220" s="11" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="B220" s="11">
         <v>4</v>
       </c>
       <c r="C220" s="12" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="D220" s="12" t="s">
         <v>6</v>
@@ -12814,13 +12853,13 @@
     </row>
     <row r="221" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A221" s="11" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="B221" s="11">
         <v>4</v>
       </c>
       <c r="C221" s="12" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="D221" s="12" t="s">
         <v>6</v>
@@ -12837,57 +12876,57 @@
     </row>
     <row r="222" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A222" s="11" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="B222" s="11">
         <v>4</v>
       </c>
       <c r="C222" s="12" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="D222" s="12" t="s">
         <v>6</v>
       </c>
       <c r="E222" s="12" t="s">
-        <v>474</v>
-      </c>
-      <c r="F222" s="12"/>
+        <v>7</v>
+      </c>
+      <c r="F222" s="12">
+        <v>1</v>
+      </c>
       <c r="G222" s="12" t="s">
-        <v>475</v>
+        <v>58</v>
       </c>
     </row>
     <row r="223" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A223" s="11" t="s">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="B223" s="11">
         <v>4</v>
       </c>
       <c r="C223" s="12" t="s">
-        <v>476</v>
+        <v>472</v>
       </c>
       <c r="D223" s="12" t="s">
         <v>6</v>
       </c>
       <c r="E223" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="F223" s="12">
-        <v>1</v>
-      </c>
+        <v>474</v>
+      </c>
+      <c r="F223" s="12"/>
       <c r="G223" s="12" t="s">
-        <v>58</v>
+        <v>475</v>
       </c>
     </row>
     <row r="224" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A224" s="11" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="B224" s="11">
         <v>4</v>
       </c>
       <c r="C224" s="12" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="D224" s="12" t="s">
         <v>6</v>
@@ -12904,13 +12943,13 @@
     </row>
     <row r="225" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A225" s="11" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="B225" s="11">
         <v>4</v>
       </c>
       <c r="C225" s="12" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="D225" s="12" t="s">
         <v>6</v>
@@ -12927,13 +12966,13 @@
     </row>
     <row r="226" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A226" s="11" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="B226" s="11">
         <v>4</v>
       </c>
       <c r="C226" s="12" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="D226" s="12" t="s">
         <v>6</v>
@@ -12950,13 +12989,13 @@
     </row>
     <row r="227" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A227" s="11" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="B227" s="11">
         <v>4</v>
       </c>
       <c r="C227" s="12" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="D227" s="12" t="s">
         <v>6</v>
@@ -12973,13 +13012,13 @@
     </row>
     <row r="228" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A228" s="11" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="B228" s="11">
         <v>4</v>
       </c>
       <c r="C228" s="12" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="D228" s="12" t="s">
         <v>6</v>
@@ -12996,13 +13035,13 @@
     </row>
     <row r="229" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A229" s="11" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="B229" s="11">
         <v>4</v>
       </c>
       <c r="C229" s="12" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="D229" s="12" t="s">
         <v>6</v>
@@ -13017,57 +13056,57 @@
         <v>58</v>
       </c>
     </row>
-    <row r="230" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A230" s="11" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="B230" s="11">
         <v>4</v>
       </c>
       <c r="C230" s="12" t="s">
+        <v>488</v>
+      </c>
+      <c r="D230" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="E230" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="F230" s="12">
+        <v>1</v>
+      </c>
+      <c r="G230" s="12" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="231" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A231" s="11" t="s">
+        <v>491</v>
+      </c>
+      <c r="B231" s="11">
+        <v>4</v>
+      </c>
+      <c r="C231" s="12" t="s">
         <v>490</v>
       </c>
-      <c r="D230" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="E230" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="F230" s="12"/>
-      <c r="G230" s="12"/>
-    </row>
-    <row r="231" spans="1:7" ht="62" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A231" s="11" t="s">
+      <c r="D231" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="E231" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="F231" s="12"/>
+      <c r="G231" s="12"/>
+    </row>
+    <row r="232" spans="1:7" ht="62" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A232" s="11" t="s">
         <v>493</v>
-      </c>
-      <c r="B231" s="11">
-        <v>5</v>
-      </c>
-      <c r="C231" s="12" t="s">
-        <v>492</v>
-      </c>
-      <c r="D231" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="E231" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="F231" s="12">
-        <v>1</v>
-      </c>
-      <c r="G231" s="12" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="232" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A232" s="11" t="s">
-        <v>495</v>
       </c>
       <c r="B232" s="11">
         <v>5</v>
       </c>
       <c r="C232" s="12" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="D232" s="12" t="s">
         <v>6</v>
@@ -13084,13 +13123,13 @@
     </row>
     <row r="233" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A233" s="11" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="B233" s="11">
         <v>5</v>
       </c>
       <c r="C233" s="12" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="D233" s="12" t="s">
         <v>6</v>
@@ -13107,13 +13146,13 @@
     </row>
     <row r="234" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A234" s="11" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="B234" s="11">
         <v>5</v>
       </c>
       <c r="C234" s="12" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="D234" s="12" t="s">
         <v>6</v>
@@ -13130,13 +13169,13 @@
     </row>
     <row r="235" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A235" s="11" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="B235" s="11">
         <v>5</v>
       </c>
       <c r="C235" s="12" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="D235" s="12" t="s">
         <v>6</v>
@@ -13153,13 +13192,13 @@
     </row>
     <row r="236" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A236" s="11" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="B236" s="11">
         <v>5</v>
       </c>
       <c r="C236" s="12" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="D236" s="12" t="s">
         <v>6</v>
@@ -13176,13 +13215,13 @@
     </row>
     <row r="237" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A237" s="11" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="B237" s="11">
         <v>5</v>
       </c>
       <c r="C237" s="12" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="D237" s="12" t="s">
         <v>6</v>
@@ -13199,13 +13238,13 @@
     </row>
     <row r="238" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A238" s="11" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="B238" s="11">
         <v>5</v>
       </c>
       <c r="C238" s="12" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="D238" s="12" t="s">
         <v>6</v>
@@ -13220,99 +13259,99 @@
         <v>58</v>
       </c>
     </row>
-    <row r="239" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A239" s="11" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="B239" s="11">
         <v>5</v>
       </c>
       <c r="C239" s="12" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="D239" s="12" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E239" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="F239" s="12"/>
-      <c r="G239" s="12"/>
-    </row>
-    <row r="240" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+        <v>7</v>
+      </c>
+      <c r="F239" s="12">
+        <v>1</v>
+      </c>
+      <c r="G239" s="12" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="240" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A240" s="11" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="B240" s="11">
         <v>5</v>
       </c>
       <c r="C240" s="12" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D240" s="12" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E240" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="F240" s="12">
-        <v>1</v>
-      </c>
-      <c r="G240" s="12" t="s">
-        <v>58</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="F240" s="12"/>
+      <c r="G240" s="12"/>
     </row>
     <row r="241" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A241" s="11" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="B241" s="11">
         <v>5</v>
       </c>
       <c r="C241" s="12" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="D241" s="12" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E241" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="F241" s="12"/>
-      <c r="G241" s="12"/>
+        <v>7</v>
+      </c>
+      <c r="F241" s="12">
+        <v>1</v>
+      </c>
+      <c r="G241" s="12" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="242" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A242" s="11" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="B242" s="11">
         <v>5</v>
       </c>
       <c r="C242" s="12" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="D242" s="12" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E242" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="F242" s="12">
-        <v>1</v>
-      </c>
-      <c r="G242" s="12" t="s">
-        <v>58</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="F242" s="12"/>
+      <c r="G242" s="12"/>
     </row>
     <row r="243" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A243" s="11" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="B243" s="11">
         <v>5</v>
       </c>
       <c r="C243" s="12" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="D243" s="12" t="s">
         <v>6</v>
@@ -13329,13 +13368,13 @@
     </row>
     <row r="244" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A244" s="11" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="B244" s="11">
         <v>5</v>
       </c>
       <c r="C244" s="12" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="D244" s="12" t="s">
         <v>6</v>
@@ -13352,13 +13391,13 @@
     </row>
     <row r="245" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A245" s="11" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="B245" s="11">
         <v>5</v>
       </c>
       <c r="C245" s="12" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="D245" s="12" t="s">
         <v>6</v>
@@ -13375,13 +13414,13 @@
     </row>
     <row r="246" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A246" s="11" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="B246" s="11">
         <v>5</v>
       </c>
       <c r="C246" s="12" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="D246" s="12" t="s">
         <v>6</v>
@@ -13398,13 +13437,13 @@
     </row>
     <row r="247" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A247" s="11" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="B247" s="11">
         <v>5</v>
       </c>
       <c r="C247" s="12" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="D247" s="12" t="s">
         <v>6</v>
@@ -13421,55 +13460,55 @@
     </row>
     <row r="248" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A248" s="11" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="B248" s="11">
         <v>5</v>
       </c>
       <c r="C248" s="12" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="D248" s="12" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E248" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="F248" s="12"/>
-      <c r="G248" s="12"/>
+        <v>7</v>
+      </c>
+      <c r="F248" s="12">
+        <v>1</v>
+      </c>
+      <c r="G248" s="12" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="249" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A249" s="11" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="B249" s="11">
         <v>5</v>
       </c>
       <c r="C249" s="12" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="D249" s="12" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E249" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="F249" s="12">
-        <v>1</v>
-      </c>
-      <c r="G249" s="12" t="s">
-        <v>58</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="F249" s="12"/>
+      <c r="G249" s="12"/>
     </row>
     <row r="250" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A250" s="11" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="B250" s="11">
         <v>5</v>
       </c>
       <c r="C250" s="12" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="D250" s="12" t="s">
         <v>6</v>
@@ -13486,13 +13525,13 @@
     </row>
     <row r="251" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A251" s="11" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="B251" s="11">
         <v>5</v>
       </c>
       <c r="C251" s="12" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="D251" s="12" t="s">
         <v>6</v>
@@ -13509,13 +13548,13 @@
     </row>
     <row r="252" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A252" s="11" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="B252" s="11">
         <v>5</v>
       </c>
       <c r="C252" s="12" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="D252" s="12" t="s">
         <v>6</v>
@@ -13532,13 +13571,13 @@
     </row>
     <row r="253" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A253" s="11" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="B253" s="11">
         <v>5</v>
       </c>
       <c r="C253" s="12" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="D253" s="12" t="s">
         <v>6</v>
@@ -13553,57 +13592,57 @@
         <v>58</v>
       </c>
     </row>
-    <row r="254" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A254" s="11" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="B254" s="11">
         <v>5</v>
       </c>
       <c r="C254" s="12" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="D254" s="12" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E254" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="F254" s="12"/>
-      <c r="G254" s="12"/>
-    </row>
-    <row r="255" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+        <v>7</v>
+      </c>
+      <c r="F254" s="12">
+        <v>1</v>
+      </c>
+      <c r="G254" s="12" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="255" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A255" s="11" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="B255" s="11">
         <v>5</v>
       </c>
       <c r="C255" s="12" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="D255" s="12" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E255" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="F255" s="12">
-        <v>1</v>
-      </c>
-      <c r="G255" s="12" t="s">
-        <v>58</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="F255" s="12"/>
+      <c r="G255" s="12"/>
     </row>
     <row r="256" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A256" s="11" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="B256" s="11">
         <v>5</v>
       </c>
       <c r="C256" s="12" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="D256" s="12" t="s">
         <v>6</v>
@@ -13620,13 +13659,13 @@
     </row>
     <row r="257" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A257" s="11" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="B257" s="11">
         <v>5</v>
       </c>
       <c r="C257" s="12" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="D257" s="12" t="s">
         <v>6</v>
@@ -13643,13 +13682,13 @@
     </row>
     <row r="258" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A258" s="11" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="B258" s="11">
         <v>5</v>
       </c>
       <c r="C258" s="12" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="D258" s="12" t="s">
         <v>6</v>
@@ -13666,13 +13705,13 @@
     </row>
     <row r="259" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A259" s="11" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="B259" s="11">
         <v>5</v>
       </c>
       <c r="C259" s="12" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="D259" s="12" t="s">
         <v>6</v>
@@ -13689,13 +13728,13 @@
     </row>
     <row r="260" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A260" s="11" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="B260" s="11">
         <v>5</v>
       </c>
       <c r="C260" s="12" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="D260" s="12" t="s">
         <v>6</v>
@@ -13712,13 +13751,13 @@
     </row>
     <row r="261" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A261" s="11" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="B261" s="11">
         <v>5</v>
       </c>
       <c r="C261" s="12" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="D261" s="12" t="s">
         <v>6</v>
@@ -13735,13 +13774,13 @@
     </row>
     <row r="262" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A262" s="11" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="B262" s="11">
         <v>5</v>
       </c>
       <c r="C262" s="12" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="D262" s="12" t="s">
         <v>6</v>
@@ -13758,13 +13797,13 @@
     </row>
     <row r="263" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A263" s="11" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="B263" s="11">
         <v>5</v>
       </c>
       <c r="C263" s="12" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="D263" s="12" t="s">
         <v>6</v>
@@ -13781,55 +13820,55 @@
     </row>
     <row r="264" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A264" s="11" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="B264" s="11">
         <v>5</v>
       </c>
       <c r="C264" s="12" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="D264" s="12" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E264" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="F264" s="12"/>
-      <c r="G264" s="12"/>
+        <v>7</v>
+      </c>
+      <c r="F264" s="12">
+        <v>1</v>
+      </c>
+      <c r="G264" s="12" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="265" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A265" s="11" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="B265" s="11">
         <v>5</v>
       </c>
       <c r="C265" s="12" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="D265" s="12" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E265" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="F265" s="12">
-        <v>1</v>
-      </c>
-      <c r="G265" s="12" t="s">
-        <v>58</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="F265" s="12"/>
+      <c r="G265" s="12"/>
     </row>
     <row r="266" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A266" s="11" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="B266" s="11">
         <v>5</v>
       </c>
       <c r="C266" s="12" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="D266" s="12" t="s">
         <v>6</v>
@@ -13846,13 +13885,13 @@
     </row>
     <row r="267" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A267" s="11" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="B267" s="11">
         <v>5</v>
       </c>
       <c r="C267" s="12" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="D267" s="12" t="s">
         <v>6</v>
@@ -13869,13 +13908,13 @@
     </row>
     <row r="268" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A268" s="11" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="B268" s="11">
         <v>5</v>
       </c>
       <c r="C268" s="12" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="D268" s="12" t="s">
         <v>6</v>
@@ -13892,13 +13931,13 @@
     </row>
     <row r="269" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A269" s="11" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="B269" s="11">
         <v>5</v>
       </c>
       <c r="C269" s="12" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="D269" s="12" t="s">
         <v>6</v>
@@ -13915,55 +13954,55 @@
     </row>
     <row r="270" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A270" s="11" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="B270" s="11">
         <v>5</v>
       </c>
       <c r="C270" s="12" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="D270" s="12" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E270" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="F270" s="12"/>
-      <c r="G270" s="12"/>
+        <v>7</v>
+      </c>
+      <c r="F270" s="12">
+        <v>1</v>
+      </c>
+      <c r="G270" s="12" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="271" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A271" s="11" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="B271" s="11">
         <v>5</v>
       </c>
       <c r="C271" s="12" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="D271" s="12" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E271" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="F271" s="12">
-        <v>1</v>
-      </c>
-      <c r="G271" s="12" t="s">
-        <v>58</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="F271" s="12"/>
+      <c r="G271" s="12"/>
     </row>
     <row r="272" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A272" s="11" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="B272" s="11">
         <v>5</v>
       </c>
       <c r="C272" s="12" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="D272" s="12" t="s">
         <v>6</v>
@@ -13980,13 +14019,13 @@
     </row>
     <row r="273" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A273" s="11" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="B273" s="11">
         <v>5</v>
       </c>
       <c r="C273" s="12" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="D273" s="12" t="s">
         <v>6</v>
@@ -14003,13 +14042,13 @@
     </row>
     <row r="274" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A274" s="11" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="B274" s="11">
         <v>5</v>
       </c>
       <c r="C274" s="12" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="D274" s="12" t="s">
         <v>6</v>
@@ -14026,13 +14065,13 @@
     </row>
     <row r="275" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A275" s="11" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="B275" s="11">
         <v>5</v>
       </c>
       <c r="C275" s="12" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="D275" s="12" t="s">
         <v>6</v>
@@ -14040,20 +14079,22 @@
       <c r="E275" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="F275" s="12"/>
+      <c r="F275" s="12">
+        <v>1</v>
+      </c>
       <c r="G275" s="12" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="276" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="276" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A276" s="11" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="B276" s="11">
         <v>5</v>
       </c>
       <c r="C276" s="12" t="s">
-        <v>1334</v>
+        <v>580</v>
       </c>
       <c r="D276" s="12" t="s">
         <v>6</v>
@@ -14061,106 +14102,104 @@
       <c r="E276" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="F276" s="12">
-        <v>1</v>
-      </c>
+      <c r="F276" s="12"/>
       <c r="G276" s="12" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="277" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="277" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A277" s="11" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="B277" s="11">
         <v>5</v>
       </c>
       <c r="C277" s="12" t="s">
-        <v>570</v>
+        <v>1334</v>
       </c>
       <c r="D277" s="12" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E277" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="F277" s="12"/>
-      <c r="G277" s="12"/>
+        <v>7</v>
+      </c>
+      <c r="F277" s="12">
+        <v>1</v>
+      </c>
+      <c r="G277" s="12" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="278" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A278" s="11" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="B278" s="11">
         <v>5</v>
       </c>
       <c r="C278" s="12" t="s">
-        <v>584</v>
+        <v>570</v>
       </c>
       <c r="D278" s="12" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E278" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="F278" s="12">
-        <v>1</v>
-      </c>
-      <c r="G278" s="12" t="s">
-        <v>58</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="F278" s="12"/>
+      <c r="G278" s="12"/>
     </row>
     <row r="279" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A279" s="11" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="B279" s="11">
         <v>5</v>
       </c>
       <c r="C279" s="12" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="D279" s="12" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E279" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="F279" s="12"/>
-      <c r="G279" s="12"/>
+        <v>7</v>
+      </c>
+      <c r="F279" s="12">
+        <v>1</v>
+      </c>
+      <c r="G279" s="12" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="280" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A280" s="11" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="B280" s="11">
         <v>5</v>
       </c>
       <c r="C280" s="12" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="D280" s="12" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E280" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="F280" s="12">
-        <v>1</v>
-      </c>
-      <c r="G280" s="12" t="s">
-        <v>58</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="F280" s="12"/>
+      <c r="G280" s="12"/>
     </row>
     <row r="281" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A281" s="11" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="B281" s="11">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C281" s="12" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="D281" s="12" t="s">
         <v>6</v>
@@ -14168,22 +14207,22 @@
       <c r="E281" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="F281" s="12" t="s">
-        <v>15</v>
+      <c r="F281" s="12">
+        <v>1</v>
       </c>
       <c r="G281" s="12" t="s">
-        <v>592</v>
+        <v>58</v>
       </c>
     </row>
     <row r="282" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A282" s="11" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="B282" s="11">
         <v>6</v>
       </c>
       <c r="C282" s="12" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="D282" s="12" t="s">
         <v>6</v>
@@ -14200,13 +14239,13 @@
     </row>
     <row r="283" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A283" s="11" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="B283" s="11">
         <v>6</v>
       </c>
       <c r="C283" s="12" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="D283" s="12" t="s">
         <v>6</v>
@@ -14223,13 +14262,13 @@
     </row>
     <row r="284" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A284" s="11" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="B284" s="11">
         <v>6</v>
       </c>
       <c r="C284" s="12" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="D284" s="12" t="s">
         <v>6</v>
@@ -14246,13 +14285,13 @@
     </row>
     <row r="285" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A285" s="11" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="B285" s="11">
         <v>6</v>
       </c>
       <c r="C285" s="12" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="D285" s="12" t="s">
         <v>6</v>
@@ -14269,13 +14308,13 @@
     </row>
     <row r="286" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A286" s="11" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="B286" s="11">
         <v>6</v>
       </c>
       <c r="C286" s="12" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="D286" s="12" t="s">
         <v>6</v>
@@ -14292,13 +14331,13 @@
     </row>
     <row r="287" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A287" s="11" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="B287" s="11">
         <v>6</v>
       </c>
       <c r="C287" s="12" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="D287" s="12" t="s">
         <v>6</v>
@@ -14315,13 +14354,13 @@
     </row>
     <row r="288" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A288" s="11" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="B288" s="11">
         <v>6</v>
       </c>
       <c r="C288" s="12" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="D288" s="12" t="s">
         <v>6</v>
@@ -14329,60 +14368,64 @@
       <c r="E288" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="F288" s="12"/>
-      <c r="G288" s="12"/>
+      <c r="F288" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="G288" s="12" t="s">
+        <v>592</v>
+      </c>
     </row>
     <row r="289" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A289" s="11" t="s">
-        <v>608</v>
+      <c r="A289" s="43" t="s">
+        <v>1364</v>
       </c>
       <c r="B289" s="11">
         <v>6</v>
       </c>
-      <c r="C289" s="12" t="s">
-        <v>607</v>
-      </c>
-      <c r="D289" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="E289" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="F289" s="12" t="s">
-        <v>296</v>
-      </c>
-      <c r="G289" s="12" t="s">
-        <v>609</v>
+      <c r="C289" s="42" t="s">
+        <v>1365</v>
+      </c>
+      <c r="D289" s="45" t="s">
+        <v>6</v>
+      </c>
+      <c r="E289" s="45" t="s">
+        <v>7</v>
+      </c>
+      <c r="F289" s="12">
+        <v>1</v>
+      </c>
+      <c r="G289" s="45" t="s">
+        <v>1363</v>
       </c>
     </row>
     <row r="290" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A290" s="11" t="s">
-        <v>611</v>
+        <v>606</v>
       </c>
       <c r="B290" s="11">
         <v>6</v>
       </c>
       <c r="C290" s="12" t="s">
-        <v>610</v>
+        <v>605</v>
       </c>
       <c r="D290" s="12" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E290" s="12" t="s">
-        <v>612</v>
+        <v>7</v>
       </c>
       <c r="F290" s="12"/>
       <c r="G290" s="12"/>
     </row>
     <row r="291" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A291" s="11" t="s">
-        <v>614</v>
+        <v>608</v>
       </c>
       <c r="B291" s="11">
         <v>6</v>
       </c>
       <c r="C291" s="12" t="s">
-        <v>613</v>
+        <v>607</v>
       </c>
       <c r="D291" s="12" t="s">
         <v>6</v>
@@ -14391,21 +14434,21 @@
         <v>7</v>
       </c>
       <c r="F291" s="12" t="s">
-        <v>15</v>
+        <v>296</v>
       </c>
       <c r="G291" s="12" t="s">
-        <v>16</v>
+        <v>609</v>
       </c>
     </row>
     <row r="292" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A292" s="11" t="s">
-        <v>616</v>
+        <v>611</v>
       </c>
       <c r="B292" s="11">
         <v>6</v>
       </c>
       <c r="C292" s="12" t="s">
-        <v>615</v>
+        <v>610</v>
       </c>
       <c r="D292" s="12" t="s">
         <v>12</v>
@@ -14416,15 +14459,15 @@
       <c r="F292" s="12"/>
       <c r="G292" s="12"/>
     </row>
-    <row r="293" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="293" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A293" s="11" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
       <c r="B293" s="11">
         <v>6</v>
       </c>
       <c r="C293" s="12" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="D293" s="12" t="s">
         <v>6</v>
@@ -14432,45 +14475,41 @@
       <c r="E293" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="F293" s="41" t="s">
-        <v>116</v>
+      <c r="F293" s="12" t="s">
+        <v>15</v>
       </c>
       <c r="G293" s="12" t="s">
-        <v>619</v>
-      </c>
-    </row>
-    <row r="294" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="294" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A294" s="11" t="s">
-        <v>621</v>
+        <v>616</v>
       </c>
       <c r="B294" s="11">
         <v>6</v>
       </c>
       <c r="C294" s="12" t="s">
-        <v>620</v>
+        <v>615</v>
       </c>
       <c r="D294" s="12" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E294" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="F294" s="12">
-        <v>1</v>
-      </c>
-      <c r="G294" s="12" t="s">
-        <v>58</v>
-      </c>
+        <v>612</v>
+      </c>
+      <c r="F294" s="12"/>
+      <c r="G294" s="12"/>
     </row>
     <row r="295" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A295" s="11" t="s">
-        <v>623</v>
+        <v>618</v>
       </c>
       <c r="B295" s="11">
         <v>6</v>
       </c>
       <c r="C295" s="12" t="s">
-        <v>622</v>
+        <v>617</v>
       </c>
       <c r="D295" s="12" t="s">
         <v>6</v>
@@ -14478,22 +14517,22 @@
       <c r="E295" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="F295" s="12">
-        <v>1</v>
+      <c r="F295" s="41" t="s">
+        <v>116</v>
       </c>
       <c r="G295" s="12" t="s">
-        <v>58</v>
+        <v>619</v>
       </c>
     </row>
     <row r="296" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A296" s="11" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="B296" s="11">
         <v>6</v>
       </c>
       <c r="C296" s="12" t="s">
-        <v>624</v>
+        <v>620</v>
       </c>
       <c r="D296" s="12" t="s">
         <v>6</v>
@@ -14510,13 +14549,13 @@
     </row>
     <row r="297" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A297" s="11" t="s">
-        <v>627</v>
+        <v>623</v>
       </c>
       <c r="B297" s="11">
         <v>6</v>
       </c>
       <c r="C297" s="12" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="D297" s="12" t="s">
         <v>6</v>
@@ -14533,13 +14572,13 @@
     </row>
     <row r="298" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A298" s="11" t="s">
-        <v>629</v>
+        <v>625</v>
       </c>
       <c r="B298" s="11">
         <v>6</v>
       </c>
       <c r="C298" s="12" t="s">
-        <v>628</v>
+        <v>624</v>
       </c>
       <c r="D298" s="12" t="s">
         <v>6</v>
@@ -14556,13 +14595,13 @@
     </row>
     <row r="299" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A299" s="11" t="s">
-        <v>631</v>
+        <v>627</v>
       </c>
       <c r="B299" s="11">
         <v>6</v>
       </c>
       <c r="C299" s="12" t="s">
-        <v>630</v>
+        <v>626</v>
       </c>
       <c r="D299" s="12" t="s">
         <v>6</v>
@@ -14579,93 +14618,97 @@
     </row>
     <row r="300" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A300" s="11" t="s">
+        <v>629</v>
+      </c>
+      <c r="B300" s="11">
+        <v>6</v>
+      </c>
+      <c r="C300" s="12" t="s">
+        <v>628</v>
+      </c>
+      <c r="D300" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="E300" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="F300" s="12">
+        <v>1</v>
+      </c>
+      <c r="G300" s="12" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="301" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A301" s="11" t="s">
+        <v>631</v>
+      </c>
+      <c r="B301" s="11">
+        <v>6</v>
+      </c>
+      <c r="C301" s="12" t="s">
+        <v>630</v>
+      </c>
+      <c r="D301" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="E301" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="F301" s="12">
+        <v>1</v>
+      </c>
+      <c r="G301" s="12" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="302" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A302" s="11" t="s">
         <v>633</v>
       </c>
-      <c r="B300" s="11">
-        <v>6</v>
-      </c>
-      <c r="C300" s="12" t="s">
+      <c r="B302" s="11">
+        <v>6</v>
+      </c>
+      <c r="C302" s="12" t="s">
         <v>632</v>
       </c>
-      <c r="D300" s="12" t="s">
+      <c r="D302" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="E300" s="12" t="s">
+      <c r="E302" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="F300" s="12"/>
-      <c r="G300" s="12"/>
-    </row>
-    <row r="301" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A301" s="11" t="s">
-        <v>635</v>
-      </c>
-      <c r="B301" s="11">
-        <v>6</v>
-      </c>
-      <c r="C301" s="12" t="s">
-        <v>634</v>
-      </c>
-      <c r="D301" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="E301" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="F301" s="12"/>
-      <c r="G301" s="12"/>
-    </row>
-    <row r="302" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A302" s="11" t="s">
-        <v>637</v>
-      </c>
-      <c r="B302" s="11">
-        <v>6</v>
-      </c>
-      <c r="C302" s="12" t="s">
-        <v>636</v>
-      </c>
-      <c r="D302" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="E302" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="F302" s="12" t="s">
-        <v>296</v>
-      </c>
-      <c r="G302" s="12" t="s">
-        <v>609</v>
-      </c>
+      <c r="F302" s="12"/>
+      <c r="G302" s="12"/>
     </row>
     <row r="303" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A303" s="11" t="s">
-        <v>639</v>
+        <v>635</v>
       </c>
       <c r="B303" s="11">
         <v>6</v>
       </c>
       <c r="C303" s="12" t="s">
-        <v>638</v>
+        <v>634</v>
       </c>
       <c r="D303" s="12" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E303" s="12" t="s">
-        <v>612</v>
+        <v>7</v>
       </c>
       <c r="F303" s="12"/>
       <c r="G303" s="12"/>
     </row>
     <row r="304" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A304" s="11" t="s">
-        <v>641</v>
+        <v>637</v>
       </c>
       <c r="B304" s="11">
         <v>6</v>
       </c>
       <c r="C304" s="12" t="s">
-        <v>640</v>
+        <v>636</v>
       </c>
       <c r="D304" s="12" t="s">
         <v>6</v>
@@ -14674,21 +14717,21 @@
         <v>7</v>
       </c>
       <c r="F304" s="12" t="s">
-        <v>15</v>
+        <v>296</v>
       </c>
       <c r="G304" s="12" t="s">
-        <v>16</v>
+        <v>609</v>
       </c>
     </row>
     <row r="305" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A305" s="11" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
       <c r="B305" s="11">
         <v>6</v>
       </c>
       <c r="C305" s="12" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="D305" s="12" t="s">
         <v>12</v>
@@ -14699,15 +14742,15 @@
       <c r="F305" s="12"/>
       <c r="G305" s="12"/>
     </row>
-    <row r="306" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="306" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A306" s="11" t="s">
-        <v>645</v>
+        <v>641</v>
       </c>
       <c r="B306" s="11">
         <v>6</v>
       </c>
       <c r="C306" s="12" t="s">
-        <v>644</v>
+        <v>640</v>
       </c>
       <c r="D306" s="12" t="s">
         <v>6</v>
@@ -14715,45 +14758,41 @@
       <c r="E306" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="F306" s="41" t="s">
-        <v>116</v>
+      <c r="F306" s="12" t="s">
+        <v>15</v>
       </c>
       <c r="G306" s="12" t="s">
-        <v>619</v>
-      </c>
-    </row>
-    <row r="307" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="307" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A307" s="11" t="s">
-        <v>647</v>
+        <v>643</v>
       </c>
       <c r="B307" s="11">
         <v>6</v>
       </c>
       <c r="C307" s="12" t="s">
-        <v>646</v>
+        <v>642</v>
       </c>
       <c r="D307" s="12" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E307" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="F307" s="12">
-        <v>1</v>
-      </c>
-      <c r="G307" s="12" t="s">
-        <v>58</v>
-      </c>
+        <v>612</v>
+      </c>
+      <c r="F307" s="12"/>
+      <c r="G307" s="12"/>
     </row>
     <row r="308" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A308" s="11" t="s">
-        <v>649</v>
+        <v>645</v>
       </c>
       <c r="B308" s="11">
         <v>6</v>
       </c>
       <c r="C308" s="12" t="s">
-        <v>648</v>
+        <v>644</v>
       </c>
       <c r="D308" s="12" t="s">
         <v>6</v>
@@ -14761,22 +14800,22 @@
       <c r="E308" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="F308" s="12">
-        <v>1</v>
+      <c r="F308" s="41" t="s">
+        <v>116</v>
       </c>
       <c r="G308" s="12" t="s">
-        <v>58</v>
+        <v>619</v>
       </c>
     </row>
     <row r="309" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A309" s="11" t="s">
-        <v>651</v>
+        <v>647</v>
       </c>
       <c r="B309" s="11">
         <v>6</v>
       </c>
       <c r="C309" s="12" t="s">
-        <v>650</v>
+        <v>646</v>
       </c>
       <c r="D309" s="12" t="s">
         <v>6</v>
@@ -14793,13 +14832,13 @@
     </row>
     <row r="310" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A310" s="11" t="s">
-        <v>653</v>
+        <v>649</v>
       </c>
       <c r="B310" s="11">
         <v>6</v>
       </c>
       <c r="C310" s="12" t="s">
-        <v>652</v>
+        <v>648</v>
       </c>
       <c r="D310" s="12" t="s">
         <v>6</v>
@@ -14816,13 +14855,13 @@
     </row>
     <row r="311" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A311" s="11" t="s">
-        <v>655</v>
+        <v>651</v>
       </c>
       <c r="B311" s="11">
         <v>6</v>
       </c>
       <c r="C311" s="12" t="s">
-        <v>654</v>
+        <v>650</v>
       </c>
       <c r="D311" s="12" t="s">
         <v>6</v>
@@ -14839,13 +14878,13 @@
     </row>
     <row r="312" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A312" s="11" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="B312" s="11">
         <v>6</v>
       </c>
       <c r="C312" s="12" t="s">
-        <v>656</v>
+        <v>652</v>
       </c>
       <c r="D312" s="12" t="s">
         <v>6</v>
@@ -14862,93 +14901,97 @@
     </row>
     <row r="313" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A313" s="11" t="s">
+        <v>655</v>
+      </c>
+      <c r="B313" s="11">
+        <v>6</v>
+      </c>
+      <c r="C313" s="12" t="s">
+        <v>654</v>
+      </c>
+      <c r="D313" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="E313" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="F313" s="12">
+        <v>1</v>
+      </c>
+      <c r="G313" s="12" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="314" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A314" s="11" t="s">
+        <v>657</v>
+      </c>
+      <c r="B314" s="11">
+        <v>6</v>
+      </c>
+      <c r="C314" s="12" t="s">
+        <v>656</v>
+      </c>
+      <c r="D314" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="E314" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="F314" s="12">
+        <v>1</v>
+      </c>
+      <c r="G314" s="12" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="315" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A315" s="11" t="s">
         <v>659</v>
       </c>
-      <c r="B313" s="11">
-        <v>6</v>
-      </c>
-      <c r="C313" s="12" t="s">
+      <c r="B315" s="11">
+        <v>6</v>
+      </c>
+      <c r="C315" s="12" t="s">
         <v>658</v>
       </c>
-      <c r="D313" s="12" t="s">
+      <c r="D315" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="E313" s="12" t="s">
+      <c r="E315" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="F313" s="12"/>
-      <c r="G313" s="12"/>
-    </row>
-    <row r="314" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A314" s="11" t="s">
-        <v>661</v>
-      </c>
-      <c r="B314" s="11">
-        <v>6</v>
-      </c>
-      <c r="C314" s="12" t="s">
-        <v>660</v>
-      </c>
-      <c r="D314" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="E314" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="F314" s="12"/>
-      <c r="G314" s="12"/>
-    </row>
-    <row r="315" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A315" s="11" t="s">
-        <v>663</v>
-      </c>
-      <c r="B315" s="11">
-        <v>6</v>
-      </c>
-      <c r="C315" s="12" t="s">
-        <v>662</v>
-      </c>
-      <c r="D315" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="E315" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="F315" s="12" t="s">
-        <v>296</v>
-      </c>
-      <c r="G315" s="12" t="s">
-        <v>609</v>
-      </c>
+      <c r="F315" s="12"/>
+      <c r="G315" s="12"/>
     </row>
     <row r="316" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A316" s="11" t="s">
-        <v>665</v>
+        <v>661</v>
       </c>
       <c r="B316" s="11">
         <v>6</v>
       </c>
       <c r="C316" s="12" t="s">
-        <v>664</v>
+        <v>660</v>
       </c>
       <c r="D316" s="12" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E316" s="12" t="s">
-        <v>612</v>
+        <v>7</v>
       </c>
       <c r="F316" s="12"/>
       <c r="G316" s="12"/>
     </row>
     <row r="317" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A317" s="11" t="s">
-        <v>667</v>
+        <v>663</v>
       </c>
       <c r="B317" s="11">
         <v>6</v>
       </c>
       <c r="C317" s="12" t="s">
-        <v>666</v>
+        <v>662</v>
       </c>
       <c r="D317" s="12" t="s">
         <v>6</v>
@@ -14957,21 +15000,21 @@
         <v>7</v>
       </c>
       <c r="F317" s="12" t="s">
-        <v>15</v>
+        <v>296</v>
       </c>
       <c r="G317" s="12" t="s">
-        <v>16</v>
+        <v>609</v>
       </c>
     </row>
     <row r="318" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A318" s="11" t="s">
-        <v>669</v>
+        <v>665</v>
       </c>
       <c r="B318" s="11">
         <v>6</v>
       </c>
       <c r="C318" s="12" t="s">
-        <v>668</v>
+        <v>664</v>
       </c>
       <c r="D318" s="12" t="s">
         <v>12</v>
@@ -14982,15 +15025,15 @@
       <c r="F318" s="12"/>
       <c r="G318" s="12"/>
     </row>
-    <row r="319" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="319" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A319" s="11" t="s">
-        <v>671</v>
+        <v>667</v>
       </c>
       <c r="B319" s="11">
         <v>6</v>
       </c>
       <c r="C319" s="12" t="s">
-        <v>670</v>
+        <v>666</v>
       </c>
       <c r="D319" s="12" t="s">
         <v>6</v>
@@ -14998,45 +15041,41 @@
       <c r="E319" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="F319" s="41" t="s">
-        <v>116</v>
+      <c r="F319" s="12" t="s">
+        <v>15</v>
       </c>
       <c r="G319" s="12" t="s">
-        <v>619</v>
-      </c>
-    </row>
-    <row r="320" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="320" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A320" s="11" t="s">
-        <v>673</v>
+        <v>669</v>
       </c>
       <c r="B320" s="11">
         <v>6</v>
       </c>
       <c r="C320" s="12" t="s">
-        <v>672</v>
+        <v>668</v>
       </c>
       <c r="D320" s="12" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E320" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="F320" s="12">
-        <v>1</v>
-      </c>
-      <c r="G320" s="12" t="s">
-        <v>58</v>
-      </c>
+        <v>612</v>
+      </c>
+      <c r="F320" s="12"/>
+      <c r="G320" s="12"/>
     </row>
     <row r="321" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A321" s="11" t="s">
-        <v>675</v>
+        <v>671</v>
       </c>
       <c r="B321" s="11">
         <v>6</v>
       </c>
       <c r="C321" s="12" t="s">
-        <v>674</v>
+        <v>670</v>
       </c>
       <c r="D321" s="12" t="s">
         <v>6</v>
@@ -15044,22 +15083,22 @@
       <c r="E321" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="F321" s="12">
-        <v>1</v>
+      <c r="F321" s="41" t="s">
+        <v>116</v>
       </c>
       <c r="G321" s="12" t="s">
-        <v>58</v>
+        <v>619</v>
       </c>
     </row>
     <row r="322" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A322" s="11" t="s">
-        <v>677</v>
+        <v>673</v>
       </c>
       <c r="B322" s="11">
         <v>6</v>
       </c>
       <c r="C322" s="12" t="s">
-        <v>676</v>
+        <v>672</v>
       </c>
       <c r="D322" s="12" t="s">
         <v>6</v>
@@ -15076,13 +15115,13 @@
     </row>
     <row r="323" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A323" s="11" t="s">
-        <v>679</v>
+        <v>675</v>
       </c>
       <c r="B323" s="11">
         <v>6</v>
       </c>
       <c r="C323" s="12" t="s">
-        <v>678</v>
+        <v>674</v>
       </c>
       <c r="D323" s="12" t="s">
         <v>6</v>
@@ -15099,13 +15138,13 @@
     </row>
     <row r="324" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A324" s="11" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="B324" s="11">
         <v>6</v>
       </c>
       <c r="C324" s="12" t="s">
-        <v>680</v>
+        <v>676</v>
       </c>
       <c r="D324" s="12" t="s">
         <v>6</v>
@@ -15122,13 +15161,13 @@
     </row>
     <row r="325" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A325" s="11" t="s">
-        <v>683</v>
+        <v>679</v>
       </c>
       <c r="B325" s="11">
         <v>6</v>
       </c>
       <c r="C325" s="12" t="s">
-        <v>682</v>
+        <v>678</v>
       </c>
       <c r="D325" s="12" t="s">
         <v>6</v>
@@ -15145,93 +15184,97 @@
     </row>
     <row r="326" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A326" s="11" t="s">
+        <v>681</v>
+      </c>
+      <c r="B326" s="11">
+        <v>6</v>
+      </c>
+      <c r="C326" s="12" t="s">
+        <v>680</v>
+      </c>
+      <c r="D326" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="E326" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="F326" s="12">
+        <v>1</v>
+      </c>
+      <c r="G326" s="12" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="327" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A327" s="11" t="s">
+        <v>683</v>
+      </c>
+      <c r="B327" s="11">
+        <v>6</v>
+      </c>
+      <c r="C327" s="12" t="s">
+        <v>682</v>
+      </c>
+      <c r="D327" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="E327" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="F327" s="12">
+        <v>1</v>
+      </c>
+      <c r="G327" s="12" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="328" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A328" s="11" t="s">
         <v>685</v>
       </c>
-      <c r="B326" s="11">
-        <v>6</v>
-      </c>
-      <c r="C326" s="12" t="s">
+      <c r="B328" s="11">
+        <v>6</v>
+      </c>
+      <c r="C328" s="12" t="s">
         <v>684</v>
       </c>
-      <c r="D326" s="12" t="s">
+      <c r="D328" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="E326" s="12" t="s">
+      <c r="E328" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="F326" s="12"/>
-      <c r="G326" s="12"/>
-    </row>
-    <row r="327" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A327" s="11" t="s">
-        <v>687</v>
-      </c>
-      <c r="B327" s="11">
-        <v>6</v>
-      </c>
-      <c r="C327" s="12" t="s">
-        <v>686</v>
-      </c>
-      <c r="D327" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="E327" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="F327" s="12"/>
-      <c r="G327" s="12"/>
-    </row>
-    <row r="328" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A328" s="11" t="s">
-        <v>689</v>
-      </c>
-      <c r="B328" s="11">
-        <v>6</v>
-      </c>
-      <c r="C328" s="12" t="s">
-        <v>688</v>
-      </c>
-      <c r="D328" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="E328" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="F328" s="12" t="s">
-        <v>296</v>
-      </c>
-      <c r="G328" s="12" t="s">
-        <v>609</v>
-      </c>
+      <c r="F328" s="12"/>
+      <c r="G328" s="12"/>
     </row>
     <row r="329" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A329" s="11" t="s">
-        <v>691</v>
+        <v>687</v>
       </c>
       <c r="B329" s="11">
         <v>6</v>
       </c>
       <c r="C329" s="12" t="s">
-        <v>690</v>
+        <v>686</v>
       </c>
       <c r="D329" s="12" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E329" s="12" t="s">
-        <v>612</v>
+        <v>7</v>
       </c>
       <c r="F329" s="12"/>
       <c r="G329" s="12"/>
     </row>
     <row r="330" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A330" s="11" t="s">
-        <v>693</v>
+        <v>689</v>
       </c>
       <c r="B330" s="11">
         <v>6</v>
       </c>
       <c r="C330" s="12" t="s">
-        <v>692</v>
+        <v>688</v>
       </c>
       <c r="D330" s="12" t="s">
         <v>6</v>
@@ -15240,21 +15283,21 @@
         <v>7</v>
       </c>
       <c r="F330" s="12" t="s">
-        <v>15</v>
+        <v>296</v>
       </c>
       <c r="G330" s="12" t="s">
-        <v>16</v>
+        <v>609</v>
       </c>
     </row>
     <row r="331" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A331" s="11" t="s">
-        <v>695</v>
+        <v>691</v>
       </c>
       <c r="B331" s="11">
         <v>6</v>
       </c>
       <c r="C331" s="12" t="s">
-        <v>694</v>
+        <v>690</v>
       </c>
       <c r="D331" s="12" t="s">
         <v>12</v>
@@ -15265,15 +15308,15 @@
       <c r="F331" s="12"/>
       <c r="G331" s="12"/>
     </row>
-    <row r="332" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="332" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A332" s="11" t="s">
-        <v>697</v>
+        <v>693</v>
       </c>
       <c r="B332" s="11">
         <v>6</v>
       </c>
       <c r="C332" s="12" t="s">
-        <v>696</v>
+        <v>692</v>
       </c>
       <c r="D332" s="12" t="s">
         <v>6</v>
@@ -15281,45 +15324,41 @@
       <c r="E332" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="F332" s="41" t="s">
-        <v>116</v>
+      <c r="F332" s="12" t="s">
+        <v>15</v>
       </c>
       <c r="G332" s="12" t="s">
-        <v>619</v>
-      </c>
-    </row>
-    <row r="333" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="333" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A333" s="11" t="s">
-        <v>699</v>
+        <v>695</v>
       </c>
       <c r="B333" s="11">
         <v>6</v>
       </c>
       <c r="C333" s="12" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
       <c r="D333" s="12" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E333" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="F333" s="12">
-        <v>1</v>
-      </c>
-      <c r="G333" s="12" t="s">
-        <v>58</v>
-      </c>
+        <v>612</v>
+      </c>
+      <c r="F333" s="12"/>
+      <c r="G333" s="12"/>
     </row>
     <row r="334" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A334" s="11" t="s">
-        <v>701</v>
+        <v>697</v>
       </c>
       <c r="B334" s="11">
         <v>6</v>
       </c>
       <c r="C334" s="12" t="s">
-        <v>700</v>
+        <v>696</v>
       </c>
       <c r="D334" s="12" t="s">
         <v>6</v>
@@ -15327,22 +15366,22 @@
       <c r="E334" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="F334" s="12">
-        <v>1</v>
+      <c r="F334" s="41" t="s">
+        <v>116</v>
       </c>
       <c r="G334" s="12" t="s">
-        <v>58</v>
+        <v>619</v>
       </c>
     </row>
     <row r="335" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A335" s="11" t="s">
-        <v>703</v>
+        <v>699</v>
       </c>
       <c r="B335" s="11">
         <v>6</v>
       </c>
       <c r="C335" s="12" t="s">
-        <v>702</v>
+        <v>698</v>
       </c>
       <c r="D335" s="12" t="s">
         <v>6</v>
@@ -15359,13 +15398,13 @@
     </row>
     <row r="336" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A336" s="11" t="s">
-        <v>705</v>
+        <v>701</v>
       </c>
       <c r="B336" s="11">
         <v>6</v>
       </c>
       <c r="C336" s="12" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="D336" s="12" t="s">
         <v>6</v>
@@ -15382,13 +15421,13 @@
     </row>
     <row r="337" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A337" s="11" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
       <c r="B337" s="11">
         <v>6</v>
       </c>
       <c r="C337" s="12" t="s">
-        <v>706</v>
+        <v>702</v>
       </c>
       <c r="D337" s="12" t="s">
         <v>6</v>
@@ -15405,13 +15444,13 @@
     </row>
     <row r="338" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A338" s="11" t="s">
-        <v>709</v>
+        <v>705</v>
       </c>
       <c r="B338" s="11">
         <v>6</v>
       </c>
       <c r="C338" s="12" t="s">
-        <v>708</v>
+        <v>704</v>
       </c>
       <c r="D338" s="12" t="s">
         <v>6</v>
@@ -15428,93 +15467,97 @@
     </row>
     <row r="339" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A339" s="11" t="s">
+        <v>707</v>
+      </c>
+      <c r="B339" s="11">
+        <v>6</v>
+      </c>
+      <c r="C339" s="12" t="s">
+        <v>706</v>
+      </c>
+      <c r="D339" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="E339" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="F339" s="12">
+        <v>1</v>
+      </c>
+      <c r="G339" s="12" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="340" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A340" s="11" t="s">
+        <v>709</v>
+      </c>
+      <c r="B340" s="11">
+        <v>6</v>
+      </c>
+      <c r="C340" s="12" t="s">
+        <v>708</v>
+      </c>
+      <c r="D340" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="E340" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="F340" s="12">
+        <v>1</v>
+      </c>
+      <c r="G340" s="12" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="341" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A341" s="11" t="s">
         <v>711</v>
       </c>
-      <c r="B339" s="11">
-        <v>6</v>
-      </c>
-      <c r="C339" s="12" t="s">
+      <c r="B341" s="11">
+        <v>6</v>
+      </c>
+      <c r="C341" s="12" t="s">
         <v>710</v>
       </c>
-      <c r="D339" s="12" t="s">
+      <c r="D341" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="E339" s="12" t="s">
+      <c r="E341" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="F339" s="12"/>
-      <c r="G339" s="12"/>
-    </row>
-    <row r="340" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A340" s="11" t="s">
-        <v>713</v>
-      </c>
-      <c r="B340" s="11">
-        <v>6</v>
-      </c>
-      <c r="C340" s="12" t="s">
-        <v>712</v>
-      </c>
-      <c r="D340" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="E340" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="F340" s="12"/>
-      <c r="G340" s="12"/>
-    </row>
-    <row r="341" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A341" s="11" t="s">
-        <v>715</v>
-      </c>
-      <c r="B341" s="11">
-        <v>6</v>
-      </c>
-      <c r="C341" s="12" t="s">
-        <v>714</v>
-      </c>
-      <c r="D341" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="E341" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="F341" s="12" t="s">
-        <v>296</v>
-      </c>
-      <c r="G341" s="12" t="s">
-        <v>609</v>
-      </c>
+      <c r="F341" s="12"/>
+      <c r="G341" s="12"/>
     </row>
     <row r="342" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A342" s="11" t="s">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="B342" s="11">
         <v>6</v>
       </c>
       <c r="C342" s="12" t="s">
-        <v>716</v>
+        <v>712</v>
       </c>
       <c r="D342" s="12" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E342" s="12" t="s">
-        <v>612</v>
+        <v>7</v>
       </c>
       <c r="F342" s="12"/>
       <c r="G342" s="12"/>
     </row>
     <row r="343" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A343" s="11" t="s">
-        <v>719</v>
+        <v>715</v>
       </c>
       <c r="B343" s="11">
         <v>6</v>
       </c>
       <c r="C343" s="12" t="s">
-        <v>718</v>
+        <v>714</v>
       </c>
       <c r="D343" s="12" t="s">
         <v>6</v>
@@ -15523,21 +15566,21 @@
         <v>7</v>
       </c>
       <c r="F343" s="12" t="s">
-        <v>15</v>
+        <v>296</v>
       </c>
       <c r="G343" s="12" t="s">
-        <v>16</v>
+        <v>609</v>
       </c>
     </row>
     <row r="344" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A344" s="11" t="s">
-        <v>721</v>
+        <v>717</v>
       </c>
       <c r="B344" s="11">
         <v>6</v>
       </c>
       <c r="C344" s="12" t="s">
-        <v>720</v>
+        <v>716</v>
       </c>
       <c r="D344" s="12" t="s">
         <v>12</v>
@@ -15548,15 +15591,15 @@
       <c r="F344" s="12"/>
       <c r="G344" s="12"/>
     </row>
-    <row r="345" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="345" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A345" s="11" t="s">
-        <v>723</v>
+        <v>719</v>
       </c>
       <c r="B345" s="11">
         <v>6</v>
       </c>
       <c r="C345" s="12" t="s">
-        <v>722</v>
+        <v>718</v>
       </c>
       <c r="D345" s="12" t="s">
         <v>6</v>
@@ -15564,45 +15607,41 @@
       <c r="E345" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="F345" s="41" t="s">
-        <v>116</v>
+      <c r="F345" s="12" t="s">
+        <v>15</v>
       </c>
       <c r="G345" s="12" t="s">
-        <v>619</v>
-      </c>
-    </row>
-    <row r="346" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="346" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A346" s="11" t="s">
-        <v>725</v>
+        <v>721</v>
       </c>
       <c r="B346" s="11">
         <v>6</v>
       </c>
       <c r="C346" s="12" t="s">
-        <v>724</v>
+        <v>720</v>
       </c>
       <c r="D346" s="12" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E346" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="F346" s="12">
-        <v>1</v>
-      </c>
-      <c r="G346" s="12" t="s">
-        <v>58</v>
-      </c>
+        <v>612</v>
+      </c>
+      <c r="F346" s="12"/>
+      <c r="G346" s="12"/>
     </row>
     <row r="347" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A347" s="11" t="s">
-        <v>727</v>
+        <v>723</v>
       </c>
       <c r="B347" s="11">
         <v>6</v>
       </c>
       <c r="C347" s="12" t="s">
-        <v>726</v>
+        <v>722</v>
       </c>
       <c r="D347" s="12" t="s">
         <v>6</v>
@@ -15610,22 +15649,22 @@
       <c r="E347" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="F347" s="12">
-        <v>1</v>
+      <c r="F347" s="41" t="s">
+        <v>116</v>
       </c>
       <c r="G347" s="12" t="s">
-        <v>58</v>
+        <v>619</v>
       </c>
     </row>
     <row r="348" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A348" s="11" t="s">
-        <v>729</v>
+        <v>725</v>
       </c>
       <c r="B348" s="11">
         <v>6</v>
       </c>
       <c r="C348" s="12" t="s">
-        <v>728</v>
+        <v>724</v>
       </c>
       <c r="D348" s="12" t="s">
         <v>6</v>
@@ -15642,13 +15681,13 @@
     </row>
     <row r="349" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A349" s="11" t="s">
-        <v>731</v>
+        <v>727</v>
       </c>
       <c r="B349" s="11">
         <v>6</v>
       </c>
       <c r="C349" s="12" t="s">
-        <v>730</v>
+        <v>726</v>
       </c>
       <c r="D349" s="12" t="s">
         <v>6</v>
@@ -15665,13 +15704,13 @@
     </row>
     <row r="350" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A350" s="11" t="s">
-        <v>733</v>
+        <v>729</v>
       </c>
       <c r="B350" s="11">
         <v>6</v>
       </c>
       <c r="C350" s="12" t="s">
-        <v>732</v>
+        <v>728</v>
       </c>
       <c r="D350" s="12" t="s">
         <v>6</v>
@@ -15688,13 +15727,13 @@
     </row>
     <row r="351" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A351" s="11" t="s">
-        <v>735</v>
+        <v>731</v>
       </c>
       <c r="B351" s="11">
         <v>6</v>
       </c>
       <c r="C351" s="12" t="s">
-        <v>734</v>
+        <v>730</v>
       </c>
       <c r="D351" s="12" t="s">
         <v>6</v>
@@ -15711,93 +15750,97 @@
     </row>
     <row r="352" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A352" s="11" t="s">
+        <v>733</v>
+      </c>
+      <c r="B352" s="11">
+        <v>6</v>
+      </c>
+      <c r="C352" s="12" t="s">
+        <v>732</v>
+      </c>
+      <c r="D352" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="E352" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="F352" s="12">
+        <v>1</v>
+      </c>
+      <c r="G352" s="12" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="353" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A353" s="11" t="s">
+        <v>735</v>
+      </c>
+      <c r="B353" s="11">
+        <v>6</v>
+      </c>
+      <c r="C353" s="12" t="s">
+        <v>734</v>
+      </c>
+      <c r="D353" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="E353" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="F353" s="12">
+        <v>1</v>
+      </c>
+      <c r="G353" s="12" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="354" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A354" s="11" t="s">
         <v>737</v>
       </c>
-      <c r="B352" s="11">
-        <v>6</v>
-      </c>
-      <c r="C352" s="12" t="s">
+      <c r="B354" s="11">
+        <v>6</v>
+      </c>
+      <c r="C354" s="12" t="s">
         <v>736</v>
       </c>
-      <c r="D352" s="12" t="s">
+      <c r="D354" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="E352" s="12" t="s">
+      <c r="E354" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="F352" s="12"/>
-      <c r="G352" s="12"/>
-    </row>
-    <row r="353" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A353" s="11" t="s">
-        <v>739</v>
-      </c>
-      <c r="B353" s="11">
-        <v>6</v>
-      </c>
-      <c r="C353" s="12" t="s">
-        <v>738</v>
-      </c>
-      <c r="D353" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="E353" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="F353" s="12"/>
-      <c r="G353" s="12"/>
-    </row>
-    <row r="354" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A354" s="11" t="s">
-        <v>741</v>
-      </c>
-      <c r="B354" s="11">
-        <v>6</v>
-      </c>
-      <c r="C354" s="12" t="s">
-        <v>740</v>
-      </c>
-      <c r="D354" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="E354" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="F354" s="12" t="s">
-        <v>296</v>
-      </c>
-      <c r="G354" s="12" t="s">
-        <v>609</v>
-      </c>
+      <c r="F354" s="12"/>
+      <c r="G354" s="12"/>
     </row>
     <row r="355" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A355" s="11" t="s">
-        <v>743</v>
+        <v>739</v>
       </c>
       <c r="B355" s="11">
         <v>6</v>
       </c>
       <c r="C355" s="12" t="s">
-        <v>742</v>
+        <v>738</v>
       </c>
       <c r="D355" s="12" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E355" s="12" t="s">
-        <v>612</v>
+        <v>7</v>
       </c>
       <c r="F355" s="12"/>
       <c r="G355" s="12"/>
     </row>
     <row r="356" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A356" s="11" t="s">
-        <v>745</v>
+        <v>741</v>
       </c>
       <c r="B356" s="11">
         <v>6</v>
       </c>
       <c r="C356" s="12" t="s">
-        <v>744</v>
+        <v>740</v>
       </c>
       <c r="D356" s="12" t="s">
         <v>6</v>
@@ -15806,21 +15849,21 @@
         <v>7</v>
       </c>
       <c r="F356" s="12" t="s">
-        <v>15</v>
+        <v>296</v>
       </c>
       <c r="G356" s="12" t="s">
-        <v>16</v>
+        <v>609</v>
       </c>
     </row>
     <row r="357" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A357" s="11" t="s">
-        <v>747</v>
+        <v>743</v>
       </c>
       <c r="B357" s="11">
         <v>6</v>
       </c>
       <c r="C357" s="12" t="s">
-        <v>746</v>
+        <v>742</v>
       </c>
       <c r="D357" s="12" t="s">
         <v>12</v>
@@ -15831,15 +15874,15 @@
       <c r="F357" s="12"/>
       <c r="G357" s="12"/>
     </row>
-    <row r="358" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="358" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A358" s="11" t="s">
-        <v>749</v>
+        <v>745</v>
       </c>
       <c r="B358" s="11">
         <v>6</v>
       </c>
       <c r="C358" s="12" t="s">
-        <v>748</v>
+        <v>744</v>
       </c>
       <c r="D358" s="12" t="s">
         <v>6</v>
@@ -15847,45 +15890,41 @@
       <c r="E358" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="F358" s="41" t="s">
-        <v>116</v>
+      <c r="F358" s="12" t="s">
+        <v>15</v>
       </c>
       <c r="G358" s="12" t="s">
-        <v>619</v>
-      </c>
-    </row>
-    <row r="359" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="359" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A359" s="11" t="s">
-        <v>751</v>
+        <v>747</v>
       </c>
       <c r="B359" s="11">
         <v>6</v>
       </c>
       <c r="C359" s="12" t="s">
-        <v>750</v>
+        <v>746</v>
       </c>
       <c r="D359" s="12" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E359" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="F359" s="12">
-        <v>1</v>
-      </c>
-      <c r="G359" s="12" t="s">
-        <v>58</v>
-      </c>
+        <v>612</v>
+      </c>
+      <c r="F359" s="12"/>
+      <c r="G359" s="12"/>
     </row>
     <row r="360" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A360" s="11" t="s">
-        <v>753</v>
+        <v>749</v>
       </c>
       <c r="B360" s="11">
         <v>6</v>
       </c>
       <c r="C360" s="12" t="s">
-        <v>752</v>
+        <v>748</v>
       </c>
       <c r="D360" s="12" t="s">
         <v>6</v>
@@ -15893,22 +15932,22 @@
       <c r="E360" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="F360" s="12">
-        <v>1</v>
+      <c r="F360" s="41" t="s">
+        <v>116</v>
       </c>
       <c r="G360" s="12" t="s">
-        <v>58</v>
+        <v>619</v>
       </c>
     </row>
     <row r="361" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A361" s="11" t="s">
-        <v>755</v>
+        <v>751</v>
       </c>
       <c r="B361" s="11">
         <v>6</v>
       </c>
       <c r="C361" s="12" t="s">
-        <v>754</v>
+        <v>750</v>
       </c>
       <c r="D361" s="12" t="s">
         <v>6</v>
@@ -15925,13 +15964,13 @@
     </row>
     <row r="362" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A362" s="11" t="s">
-        <v>757</v>
+        <v>753</v>
       </c>
       <c r="B362" s="11">
         <v>6</v>
       </c>
       <c r="C362" s="12" t="s">
-        <v>756</v>
+        <v>752</v>
       </c>
       <c r="D362" s="12" t="s">
         <v>6</v>
@@ -15948,13 +15987,13 @@
     </row>
     <row r="363" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A363" s="11" t="s">
-        <v>759</v>
+        <v>755</v>
       </c>
       <c r="B363" s="11">
         <v>6</v>
       </c>
       <c r="C363" s="12" t="s">
-        <v>758</v>
+        <v>754</v>
       </c>
       <c r="D363" s="12" t="s">
         <v>6</v>
@@ -15971,13 +16010,13 @@
     </row>
     <row r="364" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A364" s="11" t="s">
-        <v>761</v>
+        <v>757</v>
       </c>
       <c r="B364" s="11">
         <v>6</v>
       </c>
       <c r="C364" s="12" t="s">
-        <v>760</v>
+        <v>756</v>
       </c>
       <c r="D364" s="12" t="s">
         <v>6</v>
@@ -15994,112 +16033,116 @@
     </row>
     <row r="365" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A365" s="11" t="s">
+        <v>759</v>
+      </c>
+      <c r="B365" s="11">
+        <v>6</v>
+      </c>
+      <c r="C365" s="12" t="s">
+        <v>758</v>
+      </c>
+      <c r="D365" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="E365" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="F365" s="12">
+        <v>1</v>
+      </c>
+      <c r="G365" s="12" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="366" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A366" s="11" t="s">
+        <v>761</v>
+      </c>
+      <c r="B366" s="11">
+        <v>6</v>
+      </c>
+      <c r="C366" s="12" t="s">
+        <v>760</v>
+      </c>
+      <c r="D366" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="E366" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="F366" s="12">
+        <v>1</v>
+      </c>
+      <c r="G366" s="12" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="367" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A367" s="11" t="s">
         <v>763</v>
       </c>
-      <c r="B365" s="11">
-        <v>6</v>
-      </c>
-      <c r="C365" s="12" t="s">
+      <c r="B367" s="11">
+        <v>6</v>
+      </c>
+      <c r="C367" s="12" t="s">
         <v>762</v>
       </c>
-      <c r="D365" s="12" t="s">
+      <c r="D367" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="E365" s="12" t="s">
+      <c r="E367" s="12" t="s">
         <v>10</v>
-      </c>
-      <c r="F365" s="12"/>
-      <c r="G365" s="12"/>
-    </row>
-    <row r="366" spans="1:7" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A366" s="11" t="s">
-        <v>765</v>
-      </c>
-      <c r="B366" s="11">
-        <v>6</v>
-      </c>
-      <c r="C366" s="12" t="s">
-        <v>764</v>
-      </c>
-      <c r="D366" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="E366" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="F366" s="12"/>
-      <c r="G366" s="12"/>
-    </row>
-    <row r="367" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A367" s="11" t="s">
-        <v>767</v>
-      </c>
-      <c r="B367" s="11">
-        <v>6</v>
-      </c>
-      <c r="C367" s="12" t="s">
-        <v>766</v>
-      </c>
-      <c r="D367" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="E367" s="12" t="s">
-        <v>7</v>
       </c>
       <c r="F367" s="12"/>
       <c r="G367" s="12"/>
     </row>
-    <row r="368" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="368" spans="1:7" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A368" s="11" t="s">
-        <v>769</v>
+        <v>765</v>
       </c>
       <c r="B368" s="11">
         <v>6</v>
       </c>
       <c r="C368" s="12" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
       <c r="D368" s="12" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E368" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="F368" s="12" t="s">
-        <v>296</v>
-      </c>
-      <c r="G368" s="12" t="s">
-        <v>609</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="F368" s="12"/>
+      <c r="G368" s="12"/>
     </row>
     <row r="369" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A369" s="11" t="s">
-        <v>771</v>
+        <v>767</v>
       </c>
       <c r="B369" s="11">
         <v>6</v>
       </c>
       <c r="C369" s="12" t="s">
-        <v>770</v>
+        <v>766</v>
       </c>
       <c r="D369" s="12" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E369" s="12" t="s">
-        <v>612</v>
+        <v>7</v>
       </c>
       <c r="F369" s="12"/>
       <c r="G369" s="12"/>
     </row>
     <row r="370" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A370" s="11" t="s">
-        <v>773</v>
+        <v>769</v>
       </c>
       <c r="B370" s="11">
         <v>6</v>
       </c>
       <c r="C370" s="12" t="s">
-        <v>772</v>
+        <v>768</v>
       </c>
       <c r="D370" s="12" t="s">
         <v>6</v>
@@ -16108,21 +16151,21 @@
         <v>7</v>
       </c>
       <c r="F370" s="12" t="s">
-        <v>15</v>
+        <v>296</v>
       </c>
       <c r="G370" s="12" t="s">
-        <v>16</v>
+        <v>609</v>
       </c>
     </row>
     <row r="371" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A371" s="11" t="s">
-        <v>775</v>
+        <v>771</v>
       </c>
       <c r="B371" s="11">
         <v>6</v>
       </c>
       <c r="C371" s="12" t="s">
-        <v>774</v>
+        <v>770</v>
       </c>
       <c r="D371" s="12" t="s">
         <v>12</v>
@@ -16133,15 +16176,15 @@
       <c r="F371" s="12"/>
       <c r="G371" s="12"/>
     </row>
-    <row r="372" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="372" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A372" s="11" t="s">
-        <v>777</v>
+        <v>773</v>
       </c>
       <c r="B372" s="11">
         <v>6</v>
       </c>
       <c r="C372" s="12" t="s">
-        <v>776</v>
+        <v>772</v>
       </c>
       <c r="D372" s="12" t="s">
         <v>6</v>
@@ -16149,45 +16192,41 @@
       <c r="E372" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="F372" s="41" t="s">
-        <v>116</v>
+      <c r="F372" s="12" t="s">
+        <v>15</v>
       </c>
       <c r="G372" s="12" t="s">
-        <v>619</v>
-      </c>
-    </row>
-    <row r="373" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="373" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A373" s="11" t="s">
-        <v>779</v>
+        <v>775</v>
       </c>
       <c r="B373" s="11">
         <v>6</v>
       </c>
       <c r="C373" s="12" t="s">
-        <v>778</v>
+        <v>774</v>
       </c>
       <c r="D373" s="12" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E373" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="F373" s="12">
-        <v>1</v>
-      </c>
-      <c r="G373" s="12" t="s">
-        <v>58</v>
-      </c>
+        <v>612</v>
+      </c>
+      <c r="F373" s="12"/>
+      <c r="G373" s="12"/>
     </row>
     <row r="374" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A374" s="11" t="s">
-        <v>781</v>
+        <v>777</v>
       </c>
       <c r="B374" s="11">
         <v>6</v>
       </c>
       <c r="C374" s="12" t="s">
-        <v>780</v>
+        <v>776</v>
       </c>
       <c r="D374" s="12" t="s">
         <v>6</v>
@@ -16195,22 +16234,22 @@
       <c r="E374" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="F374" s="12">
-        <v>1</v>
+      <c r="F374" s="41" t="s">
+        <v>116</v>
       </c>
       <c r="G374" s="12" t="s">
-        <v>58</v>
+        <v>619</v>
       </c>
     </row>
     <row r="375" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A375" s="11" t="s">
-        <v>783</v>
+        <v>779</v>
       </c>
       <c r="B375" s="11">
         <v>6</v>
       </c>
       <c r="C375" s="12" t="s">
-        <v>782</v>
+        <v>778</v>
       </c>
       <c r="D375" s="12" t="s">
         <v>6</v>
@@ -16227,13 +16266,13 @@
     </row>
     <row r="376" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A376" s="11" t="s">
-        <v>785</v>
+        <v>781</v>
       </c>
       <c r="B376" s="11">
         <v>6</v>
       </c>
       <c r="C376" s="12" t="s">
-        <v>784</v>
+        <v>780</v>
       </c>
       <c r="D376" s="12" t="s">
         <v>6</v>
@@ -16250,13 +16289,13 @@
     </row>
     <row r="377" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A377" s="11" t="s">
-        <v>787</v>
+        <v>783</v>
       </c>
       <c r="B377" s="11">
         <v>6</v>
       </c>
       <c r="C377" s="12" t="s">
-        <v>786</v>
+        <v>782</v>
       </c>
       <c r="D377" s="12" t="s">
         <v>6</v>
@@ -16273,13 +16312,13 @@
     </row>
     <row r="378" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A378" s="11" t="s">
-        <v>789</v>
+        <v>785</v>
       </c>
       <c r="B378" s="11">
         <v>6</v>
       </c>
       <c r="C378" s="12" t="s">
-        <v>788</v>
+        <v>784</v>
       </c>
       <c r="D378" s="12" t="s">
         <v>6</v>
@@ -16296,78 +16335,78 @@
     </row>
     <row r="379" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A379" s="11" t="s">
+        <v>787</v>
+      </c>
+      <c r="B379" s="11">
+        <v>6</v>
+      </c>
+      <c r="C379" s="12" t="s">
+        <v>786</v>
+      </c>
+      <c r="D379" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="E379" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="F379" s="12">
+        <v>1</v>
+      </c>
+      <c r="G379" s="12" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="380" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A380" s="11" t="s">
+        <v>789</v>
+      </c>
+      <c r="B380" s="11">
+        <v>6</v>
+      </c>
+      <c r="C380" s="12" t="s">
+        <v>788</v>
+      </c>
+      <c r="D380" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="E380" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="F380" s="12">
+        <v>1</v>
+      </c>
+      <c r="G380" s="12" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="381" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A381" s="11" t="s">
         <v>791</v>
       </c>
-      <c r="B379" s="11">
-        <v>6</v>
-      </c>
-      <c r="C379" s="12" t="s">
+      <c r="B381" s="11">
+        <v>6</v>
+      </c>
+      <c r="C381" s="12" t="s">
         <v>790</v>
       </c>
-      <c r="D379" s="12" t="s">
+      <c r="D381" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="E379" s="12" t="s">
+      <c r="E381" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="F379" s="12"/>
-      <c r="G379" s="12"/>
-    </row>
-    <row r="380" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A380" s="11" t="s">
-        <v>793</v>
-      </c>
-      <c r="B380" s="11">
-        <v>6</v>
-      </c>
-      <c r="C380" s="12" t="s">
-        <v>792</v>
-      </c>
-      <c r="D380" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="E380" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="F380" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="G380" s="12" t="s">
-        <v>592</v>
-      </c>
-    </row>
-    <row r="381" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A381" s="11" t="s">
-        <v>795</v>
-      </c>
-      <c r="B381" s="11">
-        <v>6</v>
-      </c>
-      <c r="C381" s="12" t="s">
-        <v>794</v>
-      </c>
-      <c r="D381" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="E381" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="F381" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="G381" s="12" t="s">
-        <v>592</v>
-      </c>
+      <c r="F381" s="12"/>
+      <c r="G381" s="12"/>
     </row>
     <row r="382" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A382" s="11" t="s">
-        <v>797</v>
+        <v>793</v>
       </c>
       <c r="B382" s="11">
         <v>6</v>
       </c>
       <c r="C382" s="12" t="s">
-        <v>796</v>
+        <v>792</v>
       </c>
       <c r="D382" s="12" t="s">
         <v>6</v>
@@ -16384,13 +16423,13 @@
     </row>
     <row r="383" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A383" s="11" t="s">
-        <v>799</v>
+        <v>795</v>
       </c>
       <c r="B383" s="11">
         <v>6</v>
       </c>
       <c r="C383" s="12" t="s">
-        <v>798</v>
+        <v>794</v>
       </c>
       <c r="D383" s="12" t="s">
         <v>6</v>
@@ -16407,13 +16446,13 @@
     </row>
     <row r="384" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A384" s="11" t="s">
-        <v>801</v>
+        <v>797</v>
       </c>
       <c r="B384" s="11">
         <v>6</v>
       </c>
       <c r="C384" s="12" t="s">
-        <v>800</v>
+        <v>796</v>
       </c>
       <c r="D384" s="12" t="s">
         <v>6</v>
@@ -16430,13 +16469,13 @@
     </row>
     <row r="385" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A385" s="11" t="s">
-        <v>803</v>
+        <v>799</v>
       </c>
       <c r="B385" s="11">
         <v>6</v>
       </c>
       <c r="C385" s="12" t="s">
-        <v>802</v>
+        <v>798</v>
       </c>
       <c r="D385" s="12" t="s">
         <v>6</v>
@@ -16453,13 +16492,13 @@
     </row>
     <row r="386" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A386" s="11" t="s">
-        <v>805</v>
+        <v>801</v>
       </c>
       <c r="B386" s="11">
         <v>6</v>
       </c>
       <c r="C386" s="12" t="s">
-        <v>804</v>
+        <v>800</v>
       </c>
       <c r="D386" s="12" t="s">
         <v>6</v>
@@ -16476,13 +16515,13 @@
     </row>
     <row r="387" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A387" s="11" t="s">
-        <v>807</v>
+        <v>803</v>
       </c>
       <c r="B387" s="11">
         <v>6</v>
       </c>
       <c r="C387" s="12" t="s">
-        <v>806</v>
+        <v>802</v>
       </c>
       <c r="D387" s="12" t="s">
         <v>6</v>
@@ -16490,18 +16529,22 @@
       <c r="E387" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="F387" s="12"/>
-      <c r="G387" s="12"/>
+      <c r="F387" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="G387" s="12" t="s">
+        <v>592</v>
+      </c>
     </row>
     <row r="388" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A388" s="11" t="s">
-        <v>809</v>
+        <v>805</v>
       </c>
       <c r="B388" s="11">
         <v>6</v>
       </c>
       <c r="C388" s="12" t="s">
-        <v>808</v>
+        <v>804</v>
       </c>
       <c r="D388" s="12" t="s">
         <v>6</v>
@@ -16510,40 +16553,40 @@
         <v>7</v>
       </c>
       <c r="F388" s="12" t="s">
-        <v>296</v>
+        <v>15</v>
       </c>
       <c r="G388" s="12" t="s">
-        <v>609</v>
+        <v>592</v>
       </c>
     </row>
     <row r="389" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A389" s="11" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="B389" s="11">
         <v>6</v>
       </c>
       <c r="C389" s="12" t="s">
-        <v>810</v>
+        <v>806</v>
       </c>
       <c r="D389" s="12" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E389" s="12" t="s">
-        <v>612</v>
+        <v>7</v>
       </c>
       <c r="F389" s="12"/>
       <c r="G389" s="12"/>
     </row>
     <row r="390" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A390" s="11" t="s">
-        <v>813</v>
+        <v>809</v>
       </c>
       <c r="B390" s="11">
         <v>6</v>
       </c>
       <c r="C390" s="12" t="s">
-        <v>812</v>
+        <v>808</v>
       </c>
       <c r="D390" s="12" t="s">
         <v>6</v>
@@ -16552,21 +16595,21 @@
         <v>7</v>
       </c>
       <c r="F390" s="12" t="s">
-        <v>15</v>
+        <v>296</v>
       </c>
       <c r="G390" s="12" t="s">
-        <v>16</v>
+        <v>609</v>
       </c>
     </row>
     <row r="391" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A391" s="11" t="s">
-        <v>815</v>
+        <v>811</v>
       </c>
       <c r="B391" s="11">
         <v>6</v>
       </c>
       <c r="C391" s="12" t="s">
-        <v>814</v>
+        <v>810</v>
       </c>
       <c r="D391" s="12" t="s">
         <v>12</v>
@@ -16577,15 +16620,15 @@
       <c r="F391" s="12"/>
       <c r="G391" s="12"/>
     </row>
-    <row r="392" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="392" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A392" s="11" t="s">
-        <v>817</v>
+        <v>813</v>
       </c>
       <c r="B392" s="11">
         <v>6</v>
       </c>
       <c r="C392" s="12" t="s">
-        <v>816</v>
+        <v>812</v>
       </c>
       <c r="D392" s="12" t="s">
         <v>6</v>
@@ -16593,45 +16636,41 @@
       <c r="E392" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="F392" s="41" t="s">
-        <v>116</v>
+      <c r="F392" s="12" t="s">
+        <v>15</v>
       </c>
       <c r="G392" s="12" t="s">
-        <v>619</v>
-      </c>
-    </row>
-    <row r="393" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="393" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A393" s="11" t="s">
-        <v>819</v>
+        <v>815</v>
       </c>
       <c r="B393" s="11">
         <v>6</v>
       </c>
       <c r="C393" s="12" t="s">
-        <v>818</v>
+        <v>814</v>
       </c>
       <c r="D393" s="12" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E393" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="F393" s="12">
-        <v>1</v>
-      </c>
-      <c r="G393" s="12" t="s">
-        <v>58</v>
-      </c>
+        <v>612</v>
+      </c>
+      <c r="F393" s="12"/>
+      <c r="G393" s="12"/>
     </row>
     <row r="394" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A394" s="11" t="s">
-        <v>821</v>
+        <v>817</v>
       </c>
       <c r="B394" s="11">
         <v>6</v>
       </c>
       <c r="C394" s="12" t="s">
-        <v>820</v>
+        <v>816</v>
       </c>
       <c r="D394" s="12" t="s">
         <v>6</v>
@@ -16639,22 +16678,22 @@
       <c r="E394" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="F394" s="12">
-        <v>1</v>
+      <c r="F394" s="41" t="s">
+        <v>116</v>
       </c>
       <c r="G394" s="12" t="s">
-        <v>58</v>
+        <v>619</v>
       </c>
     </row>
     <row r="395" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A395" s="11" t="s">
-        <v>823</v>
+        <v>819</v>
       </c>
       <c r="B395" s="11">
         <v>6</v>
       </c>
       <c r="C395" s="12" t="s">
-        <v>822</v>
+        <v>818</v>
       </c>
       <c r="D395" s="12" t="s">
         <v>6</v>
@@ -16671,13 +16710,13 @@
     </row>
     <row r="396" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A396" s="11" t="s">
-        <v>825</v>
+        <v>821</v>
       </c>
       <c r="B396" s="11">
         <v>6</v>
       </c>
       <c r="C396" s="12" t="s">
-        <v>824</v>
+        <v>820</v>
       </c>
       <c r="D396" s="12" t="s">
         <v>6</v>
@@ -16694,13 +16733,13 @@
     </row>
     <row r="397" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A397" s="11" t="s">
-        <v>827</v>
+        <v>823</v>
       </c>
       <c r="B397" s="11">
         <v>6</v>
       </c>
       <c r="C397" s="12" t="s">
-        <v>826</v>
+        <v>822</v>
       </c>
       <c r="D397" s="12" t="s">
         <v>6</v>
@@ -16715,15 +16754,15 @@
         <v>58</v>
       </c>
     </row>
-    <row r="398" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="398" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A398" s="11" t="s">
-        <v>829</v>
+        <v>825</v>
       </c>
       <c r="B398" s="11">
         <v>6</v>
       </c>
       <c r="C398" s="12" t="s">
-        <v>828</v>
+        <v>824</v>
       </c>
       <c r="D398" s="12" t="s">
         <v>6</v>
@@ -16740,32 +16779,36 @@
     </row>
     <row r="399" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A399" s="11" t="s">
-        <v>831</v>
+        <v>827</v>
       </c>
       <c r="B399" s="11">
         <v>6</v>
       </c>
       <c r="C399" s="12" t="s">
-        <v>830</v>
+        <v>826</v>
       </c>
       <c r="D399" s="12" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E399" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="F399" s="12"/>
-      <c r="G399" s="12"/>
+        <v>7</v>
+      </c>
+      <c r="F399" s="12">
+        <v>1</v>
+      </c>
+      <c r="G399" s="12" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="400" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A400" s="11" t="s">
-        <v>833</v>
+        <v>829</v>
       </c>
       <c r="B400" s="11">
         <v>6</v>
       </c>
       <c r="C400" s="12" t="s">
-        <v>832</v>
+        <v>828</v>
       </c>
       <c r="D400" s="12" t="s">
         <v>6</v>
@@ -16773,60 +16816,60 @@
       <c r="E400" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="F400" s="12"/>
-      <c r="G400" s="12"/>
-    </row>
-    <row r="401" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="F400" s="12">
+        <v>1</v>
+      </c>
+      <c r="G400" s="12" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="401" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A401" s="11" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="B401" s="11">
         <v>6</v>
       </c>
       <c r="C401" s="12" t="s">
-        <v>834</v>
+        <v>830</v>
       </c>
       <c r="D401" s="12" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E401" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="F401" s="12" t="s">
-        <v>296</v>
-      </c>
-      <c r="G401" s="12" t="s">
-        <v>609</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="F401" s="12"/>
+      <c r="G401" s="12"/>
     </row>
     <row r="402" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A402" s="11" t="s">
-        <v>837</v>
+        <v>833</v>
       </c>
       <c r="B402" s="11">
         <v>6</v>
       </c>
       <c r="C402" s="12" t="s">
-        <v>836</v>
+        <v>832</v>
       </c>
       <c r="D402" s="12" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E402" s="12" t="s">
-        <v>612</v>
+        <v>7</v>
       </c>
       <c r="F402" s="12"/>
       <c r="G402" s="12"/>
     </row>
     <row r="403" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A403" s="11" t="s">
-        <v>839</v>
+        <v>835</v>
       </c>
       <c r="B403" s="11">
         <v>6</v>
       </c>
       <c r="C403" s="12" t="s">
-        <v>838</v>
+        <v>834</v>
       </c>
       <c r="D403" s="12" t="s">
         <v>6</v>
@@ -16835,21 +16878,21 @@
         <v>7</v>
       </c>
       <c r="F403" s="12" t="s">
-        <v>15</v>
+        <v>296</v>
       </c>
       <c r="G403" s="12" t="s">
-        <v>16</v>
+        <v>609</v>
       </c>
     </row>
     <row r="404" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A404" s="11" t="s">
-        <v>841</v>
+        <v>837</v>
       </c>
       <c r="B404" s="11">
         <v>6</v>
       </c>
       <c r="C404" s="12" t="s">
-        <v>840</v>
+        <v>836</v>
       </c>
       <c r="D404" s="12" t="s">
         <v>12</v>
@@ -16860,15 +16903,15 @@
       <c r="F404" s="12"/>
       <c r="G404" s="12"/>
     </row>
-    <row r="405" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="405" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A405" s="11" t="s">
-        <v>843</v>
+        <v>839</v>
       </c>
       <c r="B405" s="11">
         <v>6</v>
       </c>
       <c r="C405" s="12" t="s">
-        <v>842</v>
+        <v>838</v>
       </c>
       <c r="D405" s="12" t="s">
         <v>6</v>
@@ -16876,45 +16919,41 @@
       <c r="E405" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="F405" s="41" t="s">
-        <v>116</v>
+      <c r="F405" s="12" t="s">
+        <v>15</v>
       </c>
       <c r="G405" s="12" t="s">
-        <v>619</v>
-      </c>
-    </row>
-    <row r="406" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="406" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A406" s="11" t="s">
-        <v>845</v>
+        <v>841</v>
       </c>
       <c r="B406" s="11">
         <v>6</v>
       </c>
       <c r="C406" s="12" t="s">
-        <v>844</v>
+        <v>840</v>
       </c>
       <c r="D406" s="12" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E406" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="F406" s="12">
-        <v>1</v>
-      </c>
-      <c r="G406" s="12" t="s">
-        <v>58</v>
-      </c>
+        <v>612</v>
+      </c>
+      <c r="F406" s="12"/>
+      <c r="G406" s="12"/>
     </row>
     <row r="407" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A407" s="11" t="s">
-        <v>847</v>
+        <v>843</v>
       </c>
       <c r="B407" s="11">
         <v>6</v>
       </c>
       <c r="C407" s="12" t="s">
-        <v>846</v>
+        <v>842</v>
       </c>
       <c r="D407" s="12" t="s">
         <v>6</v>
@@ -16922,22 +16961,22 @@
       <c r="E407" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="F407" s="12">
-        <v>1</v>
+      <c r="F407" s="41" t="s">
+        <v>116</v>
       </c>
       <c r="G407" s="12" t="s">
-        <v>58</v>
+        <v>619</v>
       </c>
     </row>
     <row r="408" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A408" s="11" t="s">
-        <v>849</v>
+        <v>845</v>
       </c>
       <c r="B408" s="11">
         <v>6</v>
       </c>
       <c r="C408" s="12" t="s">
-        <v>848</v>
+        <v>844</v>
       </c>
       <c r="D408" s="12" t="s">
         <v>6</v>
@@ -16954,13 +16993,13 @@
     </row>
     <row r="409" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A409" s="11" t="s">
-        <v>851</v>
+        <v>847</v>
       </c>
       <c r="B409" s="11">
         <v>6</v>
       </c>
       <c r="C409" s="12" t="s">
-        <v>850</v>
+        <v>846</v>
       </c>
       <c r="D409" s="12" t="s">
         <v>6</v>
@@ -16977,13 +17016,13 @@
     </row>
     <row r="410" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A410" s="11" t="s">
-        <v>853</v>
+        <v>849</v>
       </c>
       <c r="B410" s="11">
         <v>6</v>
       </c>
       <c r="C410" s="12" t="s">
-        <v>852</v>
+        <v>848</v>
       </c>
       <c r="D410" s="12" t="s">
         <v>6</v>
@@ -16998,15 +17037,15 @@
         <v>58</v>
       </c>
     </row>
-    <row r="411" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="411" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A411" s="11" t="s">
-        <v>855</v>
+        <v>851</v>
       </c>
       <c r="B411" s="11">
         <v>6</v>
       </c>
       <c r="C411" s="12" t="s">
-        <v>854</v>
+        <v>850</v>
       </c>
       <c r="D411" s="12" t="s">
         <v>6</v>
@@ -17023,32 +17062,36 @@
     </row>
     <row r="412" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A412" s="11" t="s">
-        <v>857</v>
+        <v>853</v>
       </c>
       <c r="B412" s="11">
         <v>6</v>
       </c>
       <c r="C412" s="12" t="s">
-        <v>856</v>
+        <v>852</v>
       </c>
       <c r="D412" s="12" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E412" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="F412" s="12"/>
-      <c r="G412" s="12"/>
+        <v>7</v>
+      </c>
+      <c r="F412" s="12">
+        <v>1</v>
+      </c>
+      <c r="G412" s="12" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="413" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A413" s="11" t="s">
-        <v>859</v>
+        <v>855</v>
       </c>
       <c r="B413" s="11">
         <v>6</v>
       </c>
       <c r="C413" s="12" t="s">
-        <v>858</v>
+        <v>854</v>
       </c>
       <c r="D413" s="12" t="s">
         <v>6</v>
@@ -17056,60 +17099,60 @@
       <c r="E413" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="F413" s="12"/>
-      <c r="G413" s="12"/>
-    </row>
-    <row r="414" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="F413" s="12">
+        <v>1</v>
+      </c>
+      <c r="G413" s="12" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="414" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A414" s="11" t="s">
-        <v>861</v>
+        <v>857</v>
       </c>
       <c r="B414" s="11">
         <v>6</v>
       </c>
       <c r="C414" s="12" t="s">
-        <v>860</v>
+        <v>856</v>
       </c>
       <c r="D414" s="12" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E414" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="F414" s="12" t="s">
-        <v>296</v>
-      </c>
-      <c r="G414" s="12" t="s">
-        <v>609</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="F414" s="12"/>
+      <c r="G414" s="12"/>
     </row>
     <row r="415" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A415" s="11" t="s">
-        <v>863</v>
+        <v>859</v>
       </c>
       <c r="B415" s="11">
         <v>6</v>
       </c>
       <c r="C415" s="12" t="s">
-        <v>862</v>
+        <v>858</v>
       </c>
       <c r="D415" s="12" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E415" s="12" t="s">
-        <v>612</v>
+        <v>7</v>
       </c>
       <c r="F415" s="12"/>
       <c r="G415" s="12"/>
     </row>
     <row r="416" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A416" s="11" t="s">
-        <v>865</v>
+        <v>861</v>
       </c>
       <c r="B416" s="11">
         <v>6</v>
       </c>
       <c r="C416" s="12" t="s">
-        <v>864</v>
+        <v>860</v>
       </c>
       <c r="D416" s="12" t="s">
         <v>6</v>
@@ -17118,21 +17161,21 @@
         <v>7</v>
       </c>
       <c r="F416" s="12" t="s">
-        <v>15</v>
+        <v>296</v>
       </c>
       <c r="G416" s="12" t="s">
-        <v>16</v>
+        <v>609</v>
       </c>
     </row>
     <row r="417" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A417" s="11" t="s">
-        <v>867</v>
+        <v>863</v>
       </c>
       <c r="B417" s="11">
         <v>6</v>
       </c>
       <c r="C417" s="12" t="s">
-        <v>866</v>
+        <v>862</v>
       </c>
       <c r="D417" s="12" t="s">
         <v>12</v>
@@ -17143,15 +17186,15 @@
       <c r="F417" s="12"/>
       <c r="G417" s="12"/>
     </row>
-    <row r="418" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="418" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A418" s="11" t="s">
-        <v>869</v>
+        <v>865</v>
       </c>
       <c r="B418" s="11">
         <v>6</v>
       </c>
       <c r="C418" s="12" t="s">
-        <v>868</v>
+        <v>864</v>
       </c>
       <c r="D418" s="12" t="s">
         <v>6</v>
@@ -17159,45 +17202,41 @@
       <c r="E418" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="F418" s="41" t="s">
-        <v>116</v>
+      <c r="F418" s="12" t="s">
+        <v>15</v>
       </c>
       <c r="G418" s="12" t="s">
-        <v>619</v>
-      </c>
-    </row>
-    <row r="419" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="419" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A419" s="11" t="s">
-        <v>871</v>
+        <v>867</v>
       </c>
       <c r="B419" s="11">
         <v>6</v>
       </c>
       <c r="C419" s="12" t="s">
-        <v>870</v>
+        <v>866</v>
       </c>
       <c r="D419" s="12" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E419" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="F419" s="12">
-        <v>1</v>
-      </c>
-      <c r="G419" s="12" t="s">
-        <v>58</v>
-      </c>
+        <v>612</v>
+      </c>
+      <c r="F419" s="12"/>
+      <c r="G419" s="12"/>
     </row>
     <row r="420" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A420" s="11" t="s">
-        <v>873</v>
+        <v>869</v>
       </c>
       <c r="B420" s="11">
         <v>6</v>
       </c>
       <c r="C420" s="12" t="s">
-        <v>872</v>
+        <v>868</v>
       </c>
       <c r="D420" s="12" t="s">
         <v>6</v>
@@ -17205,22 +17244,22 @@
       <c r="E420" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="F420" s="12">
-        <v>1</v>
+      <c r="F420" s="41" t="s">
+        <v>116</v>
       </c>
       <c r="G420" s="12" t="s">
-        <v>58</v>
+        <v>619</v>
       </c>
     </row>
     <row r="421" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A421" s="11" t="s">
-        <v>875</v>
+        <v>871</v>
       </c>
       <c r="B421" s="11">
         <v>6</v>
       </c>
       <c r="C421" s="12" t="s">
-        <v>874</v>
+        <v>870</v>
       </c>
       <c r="D421" s="12" t="s">
         <v>6</v>
@@ -17237,13 +17276,13 @@
     </row>
     <row r="422" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A422" s="11" t="s">
-        <v>877</v>
+        <v>873</v>
       </c>
       <c r="B422" s="11">
         <v>6</v>
       </c>
       <c r="C422" s="12" t="s">
-        <v>876</v>
+        <v>872</v>
       </c>
       <c r="D422" s="12" t="s">
         <v>6</v>
@@ -17260,13 +17299,13 @@
     </row>
     <row r="423" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A423" s="11" t="s">
-        <v>879</v>
+        <v>875</v>
       </c>
       <c r="B423" s="11">
         <v>6</v>
       </c>
       <c r="C423" s="12" t="s">
-        <v>878</v>
+        <v>874</v>
       </c>
       <c r="D423" s="12" t="s">
         <v>6</v>
@@ -17283,13 +17322,13 @@
     </row>
     <row r="424" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A424" s="11" t="s">
-        <v>881</v>
+        <v>877</v>
       </c>
       <c r="B424" s="11">
         <v>6</v>
       </c>
       <c r="C424" s="12" t="s">
-        <v>880</v>
+        <v>876</v>
       </c>
       <c r="D424" s="12" t="s">
         <v>6</v>
@@ -17306,32 +17345,36 @@
     </row>
     <row r="425" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A425" s="11" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
       <c r="B425" s="11">
         <v>6</v>
       </c>
       <c r="C425" s="12" t="s">
-        <v>882</v>
+        <v>878</v>
       </c>
       <c r="D425" s="12" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E425" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="F425" s="12"/>
-      <c r="G425" s="12"/>
+        <v>7</v>
+      </c>
+      <c r="F425" s="12">
+        <v>1</v>
+      </c>
+      <c r="G425" s="12" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="426" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A426" s="11" t="s">
-        <v>885</v>
+        <v>881</v>
       </c>
       <c r="B426" s="11">
         <v>6</v>
       </c>
       <c r="C426" s="12" t="s">
-        <v>884</v>
+        <v>880</v>
       </c>
       <c r="D426" s="12" t="s">
         <v>6</v>
@@ -17339,60 +17382,60 @@
       <c r="E426" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="F426" s="12"/>
-      <c r="G426" s="12"/>
+      <c r="F426" s="12">
+        <v>1</v>
+      </c>
+      <c r="G426" s="12" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="427" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A427" s="11" t="s">
-        <v>887</v>
+        <v>883</v>
       </c>
       <c r="B427" s="11">
         <v>6</v>
       </c>
       <c r="C427" s="12" t="s">
-        <v>886</v>
+        <v>882</v>
       </c>
       <c r="D427" s="12" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E427" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="F427" s="12" t="s">
-        <v>296</v>
-      </c>
-      <c r="G427" s="12" t="s">
-        <v>609</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="F427" s="12"/>
+      <c r="G427" s="12"/>
     </row>
     <row r="428" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A428" s="11" t="s">
-        <v>889</v>
+        <v>885</v>
       </c>
       <c r="B428" s="11">
         <v>6</v>
       </c>
       <c r="C428" s="12" t="s">
-        <v>888</v>
+        <v>884</v>
       </c>
       <c r="D428" s="12" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E428" s="12" t="s">
-        <v>612</v>
+        <v>7</v>
       </c>
       <c r="F428" s="12"/>
       <c r="G428" s="12"/>
     </row>
-    <row r="429" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="429" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A429" s="11" t="s">
-        <v>891</v>
+        <v>887</v>
       </c>
       <c r="B429" s="11">
         <v>6</v>
       </c>
       <c r="C429" s="12" t="s">
-        <v>890</v>
+        <v>886</v>
       </c>
       <c r="D429" s="12" t="s">
         <v>6</v>
@@ -17401,21 +17444,21 @@
         <v>7</v>
       </c>
       <c r="F429" s="12" t="s">
-        <v>15</v>
+        <v>296</v>
       </c>
       <c r="G429" s="12" t="s">
-        <v>16</v>
+        <v>609</v>
       </c>
     </row>
     <row r="430" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A430" s="11" t="s">
-        <v>893</v>
+        <v>889</v>
       </c>
       <c r="B430" s="11">
         <v>6</v>
       </c>
       <c r="C430" s="12" t="s">
-        <v>892</v>
+        <v>888</v>
       </c>
       <c r="D430" s="12" t="s">
         <v>12</v>
@@ -17426,15 +17469,15 @@
       <c r="F430" s="12"/>
       <c r="G430" s="12"/>
     </row>
-    <row r="431" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="431" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A431" s="11" t="s">
-        <v>895</v>
+        <v>891</v>
       </c>
       <c r="B431" s="11">
         <v>6</v>
       </c>
       <c r="C431" s="12" t="s">
-        <v>894</v>
+        <v>890</v>
       </c>
       <c r="D431" s="12" t="s">
         <v>6</v>
@@ -17442,45 +17485,41 @@
       <c r="E431" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="F431" s="41" t="s">
-        <v>116</v>
+      <c r="F431" s="12" t="s">
+        <v>15</v>
       </c>
       <c r="G431" s="12" t="s">
-        <v>619</v>
+        <v>16</v>
       </c>
     </row>
     <row r="432" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A432" s="11" t="s">
-        <v>897</v>
+        <v>893</v>
       </c>
       <c r="B432" s="11">
         <v>6</v>
       </c>
       <c r="C432" s="12" t="s">
-        <v>896</v>
+        <v>892</v>
       </c>
       <c r="D432" s="12" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E432" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="F432" s="12">
-        <v>1</v>
-      </c>
-      <c r="G432" s="12" t="s">
-        <v>58</v>
-      </c>
+        <v>612</v>
+      </c>
+      <c r="F432" s="12"/>
+      <c r="G432" s="12"/>
     </row>
     <row r="433" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A433" s="11" t="s">
-        <v>899</v>
+        <v>895</v>
       </c>
       <c r="B433" s="11">
         <v>6</v>
       </c>
       <c r="C433" s="12" t="s">
-        <v>898</v>
+        <v>894</v>
       </c>
       <c r="D433" s="12" t="s">
         <v>6</v>
@@ -17488,22 +17527,22 @@
       <c r="E433" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="F433" s="12">
-        <v>1</v>
+      <c r="F433" s="41" t="s">
+        <v>116</v>
       </c>
       <c r="G433" s="12" t="s">
-        <v>58</v>
+        <v>619</v>
       </c>
     </row>
     <row r="434" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A434" s="11" t="s">
-        <v>901</v>
+        <v>897</v>
       </c>
       <c r="B434" s="11">
         <v>6</v>
       </c>
       <c r="C434" s="12" t="s">
-        <v>900</v>
+        <v>896</v>
       </c>
       <c r="D434" s="12" t="s">
         <v>6</v>
@@ -17520,13 +17559,13 @@
     </row>
     <row r="435" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A435" s="11" t="s">
-        <v>903</v>
+        <v>899</v>
       </c>
       <c r="B435" s="11">
         <v>6</v>
       </c>
       <c r="C435" s="12" t="s">
-        <v>902</v>
+        <v>898</v>
       </c>
       <c r="D435" s="12" t="s">
         <v>6</v>
@@ -17543,13 +17582,13 @@
     </row>
     <row r="436" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A436" s="11" t="s">
-        <v>905</v>
+        <v>901</v>
       </c>
       <c r="B436" s="11">
         <v>6</v>
       </c>
       <c r="C436" s="12" t="s">
-        <v>904</v>
+        <v>900</v>
       </c>
       <c r="D436" s="12" t="s">
         <v>6</v>
@@ -17566,13 +17605,13 @@
     </row>
     <row r="437" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A437" s="11" t="s">
-        <v>907</v>
+        <v>903</v>
       </c>
       <c r="B437" s="11">
         <v>6</v>
       </c>
       <c r="C437" s="12" t="s">
-        <v>906</v>
+        <v>902</v>
       </c>
       <c r="D437" s="12" t="s">
         <v>6</v>
@@ -17589,93 +17628,97 @@
     </row>
     <row r="438" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A438" s="11" t="s">
+        <v>905</v>
+      </c>
+      <c r="B438" s="11">
+        <v>6</v>
+      </c>
+      <c r="C438" s="12" t="s">
+        <v>904</v>
+      </c>
+      <c r="D438" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="E438" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="F438" s="12">
+        <v>1</v>
+      </c>
+      <c r="G438" s="12" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="439" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A439" s="11" t="s">
+        <v>907</v>
+      </c>
+      <c r="B439" s="11">
+        <v>6</v>
+      </c>
+      <c r="C439" s="12" t="s">
+        <v>906</v>
+      </c>
+      <c r="D439" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="E439" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="F439" s="12">
+        <v>1</v>
+      </c>
+      <c r="G439" s="12" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="440" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A440" s="11" t="s">
         <v>909</v>
       </c>
-      <c r="B438" s="11">
-        <v>6</v>
-      </c>
-      <c r="C438" s="12" t="s">
+      <c r="B440" s="11">
+        <v>6</v>
+      </c>
+      <c r="C440" s="12" t="s">
         <v>908</v>
       </c>
-      <c r="D438" s="12" t="s">
+      <c r="D440" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="E438" s="12" t="s">
+      <c r="E440" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="F438" s="12"/>
-      <c r="G438" s="12"/>
-    </row>
-    <row r="439" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A439" s="11" t="s">
-        <v>911</v>
-      </c>
-      <c r="B439" s="11">
-        <v>6</v>
-      </c>
-      <c r="C439" s="12" t="s">
-        <v>910</v>
-      </c>
-      <c r="D439" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="E439" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="F439" s="12"/>
-      <c r="G439" s="12"/>
-    </row>
-    <row r="440" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A440" s="11" t="s">
-        <v>913</v>
-      </c>
-      <c r="B440" s="11">
-        <v>6</v>
-      </c>
-      <c r="C440" s="12" t="s">
-        <v>912</v>
-      </c>
-      <c r="D440" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="E440" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="F440" s="12" t="s">
-        <v>296</v>
-      </c>
-      <c r="G440" s="12" t="s">
-        <v>609</v>
-      </c>
+      <c r="F440" s="12"/>
+      <c r="G440" s="12"/>
     </row>
     <row r="441" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A441" s="11" t="s">
-        <v>915</v>
+        <v>911</v>
       </c>
       <c r="B441" s="11">
         <v>6</v>
       </c>
       <c r="C441" s="12" t="s">
-        <v>914</v>
+        <v>910</v>
       </c>
       <c r="D441" s="12" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E441" s="12" t="s">
-        <v>612</v>
+        <v>7</v>
       </c>
       <c r="F441" s="12"/>
       <c r="G441" s="12"/>
     </row>
     <row r="442" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A442" s="11" t="s">
-        <v>917</v>
+        <v>913</v>
       </c>
       <c r="B442" s="11">
         <v>6</v>
       </c>
       <c r="C442" s="12" t="s">
-        <v>916</v>
+        <v>912</v>
       </c>
       <c r="D442" s="12" t="s">
         <v>6</v>
@@ -17684,21 +17727,21 @@
         <v>7</v>
       </c>
       <c r="F442" s="12" t="s">
-        <v>15</v>
+        <v>296</v>
       </c>
       <c r="G442" s="12" t="s">
-        <v>16</v>
+        <v>609</v>
       </c>
     </row>
     <row r="443" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A443" s="11" t="s">
-        <v>919</v>
+        <v>915</v>
       </c>
       <c r="B443" s="11">
         <v>6</v>
       </c>
       <c r="C443" s="12" t="s">
-        <v>918</v>
+        <v>914</v>
       </c>
       <c r="D443" s="12" t="s">
         <v>12</v>
@@ -17709,15 +17752,15 @@
       <c r="F443" s="12"/>
       <c r="G443" s="12"/>
     </row>
-    <row r="444" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="444" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A444" s="11" t="s">
-        <v>921</v>
+        <v>917</v>
       </c>
       <c r="B444" s="11">
         <v>6</v>
       </c>
       <c r="C444" s="12" t="s">
-        <v>920</v>
+        <v>916</v>
       </c>
       <c r="D444" s="12" t="s">
         <v>6</v>
@@ -17725,45 +17768,41 @@
       <c r="E444" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="F444" s="41" t="s">
-        <v>116</v>
+      <c r="F444" s="12" t="s">
+        <v>15</v>
       </c>
       <c r="G444" s="12" t="s">
-        <v>619</v>
-      </c>
-    </row>
-    <row r="445" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="445" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A445" s="11" t="s">
-        <v>923</v>
+        <v>919</v>
       </c>
       <c r="B445" s="11">
         <v>6</v>
       </c>
       <c r="C445" s="12" t="s">
-        <v>922</v>
+        <v>918</v>
       </c>
       <c r="D445" s="12" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E445" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="F445" s="12">
-        <v>1</v>
-      </c>
-      <c r="G445" s="12" t="s">
-        <v>58</v>
-      </c>
+        <v>612</v>
+      </c>
+      <c r="F445" s="12"/>
+      <c r="G445" s="12"/>
     </row>
     <row r="446" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A446" s="11" t="s">
-        <v>925</v>
+        <v>921</v>
       </c>
       <c r="B446" s="11">
         <v>6</v>
       </c>
       <c r="C446" s="12" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="D446" s="12" t="s">
         <v>6</v>
@@ -17771,22 +17810,22 @@
       <c r="E446" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="F446" s="12">
-        <v>1</v>
+      <c r="F446" s="41" t="s">
+        <v>116</v>
       </c>
       <c r="G446" s="12" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="447" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="447" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A447" s="11" t="s">
-        <v>927</v>
+        <v>923</v>
       </c>
       <c r="B447" s="11">
         <v>6</v>
       </c>
       <c r="C447" s="12" t="s">
-        <v>926</v>
+        <v>922</v>
       </c>
       <c r="D447" s="12" t="s">
         <v>6</v>
@@ -17803,13 +17842,13 @@
     </row>
     <row r="448" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A448" s="11" t="s">
-        <v>929</v>
+        <v>925</v>
       </c>
       <c r="B448" s="11">
         <v>6</v>
       </c>
       <c r="C448" s="12" t="s">
-        <v>928</v>
+        <v>924</v>
       </c>
       <c r="D448" s="12" t="s">
         <v>6</v>
@@ -17826,78 +17865,82 @@
     </row>
     <row r="449" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A449" s="11" t="s">
+        <v>927</v>
+      </c>
+      <c r="B449" s="11">
+        <v>6</v>
+      </c>
+      <c r="C449" s="12" t="s">
+        <v>926</v>
+      </c>
+      <c r="D449" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="E449" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="F449" s="12">
+        <v>1</v>
+      </c>
+      <c r="G449" s="12" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="450" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A450" s="11" t="s">
+        <v>929</v>
+      </c>
+      <c r="B450" s="11">
+        <v>6</v>
+      </c>
+      <c r="C450" s="12" t="s">
+        <v>928</v>
+      </c>
+      <c r="D450" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="E450" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="F450" s="12">
+        <v>1</v>
+      </c>
+      <c r="G450" s="12" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="451" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A451" s="11" t="s">
         <v>931</v>
       </c>
-      <c r="B449" s="11">
-        <v>6</v>
-      </c>
-      <c r="C449" s="12" t="s">
+      <c r="B451" s="11">
+        <v>6</v>
+      </c>
+      <c r="C451" s="12" t="s">
         <v>930</v>
       </c>
-      <c r="D449" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="E449" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="F449" s="12">
-        <v>1</v>
-      </c>
-      <c r="G449" s="12" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="450" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A450" s="11" t="s">
-        <v>933</v>
-      </c>
-      <c r="B450" s="11">
-        <v>6</v>
-      </c>
-      <c r="C450" s="12" t="s">
-        <v>932</v>
-      </c>
-      <c r="D450" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="E450" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="F450" s="12">
-        <v>1</v>
-      </c>
-      <c r="G450" s="12" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="451" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A451" s="11" t="s">
-        <v>935</v>
-      </c>
-      <c r="B451" s="11">
-        <v>6</v>
-      </c>
-      <c r="C451" s="12" t="s">
-        <v>934</v>
-      </c>
       <c r="D451" s="12" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E451" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="F451" s="12"/>
-      <c r="G451" s="12"/>
+        <v>7</v>
+      </c>
+      <c r="F451" s="12">
+        <v>1</v>
+      </c>
+      <c r="G451" s="12" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="452" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A452" s="11" t="s">
-        <v>937</v>
+        <v>933</v>
       </c>
       <c r="B452" s="11">
         <v>6</v>
       </c>
       <c r="C452" s="12" t="s">
-        <v>936</v>
+        <v>932</v>
       </c>
       <c r="D452" s="12" t="s">
         <v>6</v>
@@ -17905,60 +17948,60 @@
       <c r="E452" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="F452" s="12"/>
-      <c r="G452" s="12"/>
-    </row>
-    <row r="453" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="F452" s="12">
+        <v>1</v>
+      </c>
+      <c r="G452" s="12" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="453" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A453" s="11" t="s">
-        <v>939</v>
+        <v>935</v>
       </c>
       <c r="B453" s="11">
         <v>6</v>
       </c>
       <c r="C453" s="12" t="s">
-        <v>938</v>
+        <v>934</v>
       </c>
       <c r="D453" s="12" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E453" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="F453" s="12" t="s">
-        <v>296</v>
-      </c>
-      <c r="G453" s="12" t="s">
-        <v>609</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="F453" s="12"/>
+      <c r="G453" s="12"/>
     </row>
     <row r="454" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A454" s="11" t="s">
-        <v>941</v>
+        <v>937</v>
       </c>
       <c r="B454" s="11">
         <v>6</v>
       </c>
       <c r="C454" s="12" t="s">
-        <v>940</v>
+        <v>936</v>
       </c>
       <c r="D454" s="12" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E454" s="12" t="s">
-        <v>612</v>
+        <v>7</v>
       </c>
       <c r="F454" s="12"/>
       <c r="G454" s="12"/>
     </row>
     <row r="455" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A455" s="11" t="s">
-        <v>943</v>
+        <v>939</v>
       </c>
       <c r="B455" s="11">
         <v>6</v>
       </c>
       <c r="C455" s="12" t="s">
-        <v>942</v>
+        <v>938</v>
       </c>
       <c r="D455" s="12" t="s">
         <v>6</v>
@@ -17967,21 +18010,21 @@
         <v>7</v>
       </c>
       <c r="F455" s="12" t="s">
-        <v>15</v>
+        <v>296</v>
       </c>
       <c r="G455" s="12" t="s">
-        <v>16</v>
+        <v>609</v>
       </c>
     </row>
     <row r="456" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A456" s="11" t="s">
-        <v>945</v>
+        <v>941</v>
       </c>
       <c r="B456" s="11">
         <v>6</v>
       </c>
       <c r="C456" s="12" t="s">
-        <v>944</v>
+        <v>940</v>
       </c>
       <c r="D456" s="12" t="s">
         <v>12</v>
@@ -17992,15 +18035,15 @@
       <c r="F456" s="12"/>
       <c r="G456" s="12"/>
     </row>
-    <row r="457" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="457" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A457" s="11" t="s">
-        <v>947</v>
+        <v>943</v>
       </c>
       <c r="B457" s="11">
         <v>6</v>
       </c>
       <c r="C457" s="12" t="s">
-        <v>946</v>
+        <v>942</v>
       </c>
       <c r="D457" s="12" t="s">
         <v>6</v>
@@ -18008,45 +18051,41 @@
       <c r="E457" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="F457" s="41" t="s">
-        <v>116</v>
+      <c r="F457" s="12" t="s">
+        <v>15</v>
       </c>
       <c r="G457" s="12" t="s">
-        <v>619</v>
-      </c>
-    </row>
-    <row r="458" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="458" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A458" s="11" t="s">
-        <v>949</v>
+        <v>945</v>
       </c>
       <c r="B458" s="11">
         <v>6</v>
       </c>
       <c r="C458" s="12" t="s">
-        <v>948</v>
+        <v>944</v>
       </c>
       <c r="D458" s="12" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E458" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="F458" s="12">
-        <v>1</v>
-      </c>
-      <c r="G458" s="12" t="s">
-        <v>58</v>
-      </c>
+        <v>612</v>
+      </c>
+      <c r="F458" s="12"/>
+      <c r="G458" s="12"/>
     </row>
     <row r="459" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A459" s="11" t="s">
-        <v>951</v>
+        <v>947</v>
       </c>
       <c r="B459" s="11">
         <v>6</v>
       </c>
       <c r="C459" s="12" t="s">
-        <v>950</v>
+        <v>946</v>
       </c>
       <c r="D459" s="12" t="s">
         <v>6</v>
@@ -18054,22 +18093,22 @@
       <c r="E459" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="F459" s="12">
-        <v>1</v>
+      <c r="F459" s="41" t="s">
+        <v>116</v>
       </c>
       <c r="G459" s="12" t="s">
-        <v>58</v>
+        <v>619</v>
       </c>
     </row>
     <row r="460" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A460" s="11" t="s">
-        <v>953</v>
+        <v>949</v>
       </c>
       <c r="B460" s="11">
         <v>6</v>
       </c>
       <c r="C460" s="12" t="s">
-        <v>952</v>
+        <v>948</v>
       </c>
       <c r="D460" s="12" t="s">
         <v>6</v>
@@ -18086,13 +18125,13 @@
     </row>
     <row r="461" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A461" s="11" t="s">
-        <v>955</v>
+        <v>951</v>
       </c>
       <c r="B461" s="11">
         <v>6</v>
       </c>
       <c r="C461" s="12" t="s">
-        <v>954</v>
+        <v>950</v>
       </c>
       <c r="D461" s="12" t="s">
         <v>6</v>
@@ -18109,13 +18148,13 @@
     </row>
     <row r="462" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A462" s="11" t="s">
-        <v>957</v>
+        <v>953</v>
       </c>
       <c r="B462" s="11">
         <v>6</v>
       </c>
       <c r="C462" s="12" t="s">
-        <v>956</v>
+        <v>952</v>
       </c>
       <c r="D462" s="12" t="s">
         <v>6</v>
@@ -18132,13 +18171,13 @@
     </row>
     <row r="463" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A463" s="11" t="s">
-        <v>959</v>
+        <v>955</v>
       </c>
       <c r="B463" s="11">
         <v>6</v>
       </c>
       <c r="C463" s="12" t="s">
-        <v>958</v>
+        <v>954</v>
       </c>
       <c r="D463" s="12" t="s">
         <v>6</v>
@@ -18155,112 +18194,116 @@
     </row>
     <row r="464" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A464" s="11" t="s">
+        <v>957</v>
+      </c>
+      <c r="B464" s="11">
+        <v>6</v>
+      </c>
+      <c r="C464" s="12" t="s">
+        <v>956</v>
+      </c>
+      <c r="D464" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="E464" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="F464" s="12">
+        <v>1</v>
+      </c>
+      <c r="G464" s="12" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="465" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A465" s="11" t="s">
+        <v>959</v>
+      </c>
+      <c r="B465" s="11">
+        <v>6</v>
+      </c>
+      <c r="C465" s="12" t="s">
+        <v>958</v>
+      </c>
+      <c r="D465" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="E465" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="F465" s="12">
+        <v>1</v>
+      </c>
+      <c r="G465" s="12" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="466" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A466" s="11" t="s">
         <v>961</v>
       </c>
-      <c r="B464" s="11">
-        <v>6</v>
-      </c>
-      <c r="C464" s="12" t="s">
+      <c r="B466" s="11">
+        <v>6</v>
+      </c>
+      <c r="C466" s="12" t="s">
         <v>960</v>
       </c>
-      <c r="D464" s="12" t="s">
+      <c r="D466" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="E464" s="12" t="s">
+      <c r="E466" s="12" t="s">
         <v>10</v>
-      </c>
-      <c r="F464" s="12"/>
-      <c r="G464" s="12"/>
-    </row>
-    <row r="465" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A465" s="11" t="s">
-        <v>963</v>
-      </c>
-      <c r="B465" s="11">
-        <v>6</v>
-      </c>
-      <c r="C465" s="12" t="s">
-        <v>962</v>
-      </c>
-      <c r="D465" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="E465" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="F465" s="12"/>
-      <c r="G465" s="12"/>
-    </row>
-    <row r="466" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A466" s="11" t="s">
-        <v>965</v>
-      </c>
-      <c r="B466" s="11">
-        <v>6</v>
-      </c>
-      <c r="C466" s="12" t="s">
-        <v>964</v>
-      </c>
-      <c r="D466" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="E466" s="12" t="s">
-        <v>7</v>
       </c>
       <c r="F466" s="12"/>
       <c r="G466" s="12"/>
     </row>
-    <row r="467" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="467" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A467" s="11" t="s">
-        <v>967</v>
+        <v>963</v>
       </c>
       <c r="B467" s="11">
         <v>6</v>
       </c>
       <c r="C467" s="12" t="s">
-        <v>966</v>
+        <v>962</v>
       </c>
       <c r="D467" s="12" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E467" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="F467" s="12" t="s">
-        <v>296</v>
-      </c>
-      <c r="G467" s="12" t="s">
-        <v>609</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="F467" s="12"/>
+      <c r="G467" s="12"/>
     </row>
     <row r="468" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A468" s="11" t="s">
-        <v>969</v>
+        <v>965</v>
       </c>
       <c r="B468" s="11">
         <v>6</v>
       </c>
       <c r="C468" s="12" t="s">
-        <v>968</v>
+        <v>964</v>
       </c>
       <c r="D468" s="12" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E468" s="12" t="s">
-        <v>612</v>
+        <v>7</v>
       </c>
       <c r="F468" s="12"/>
       <c r="G468" s="12"/>
     </row>
     <row r="469" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A469" s="11" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="B469" s="11">
         <v>6</v>
       </c>
       <c r="C469" s="12" t="s">
-        <v>970</v>
+        <v>966</v>
       </c>
       <c r="D469" s="12" t="s">
         <v>6</v>
@@ -18269,21 +18312,21 @@
         <v>7</v>
       </c>
       <c r="F469" s="12" t="s">
-        <v>15</v>
+        <v>296</v>
       </c>
       <c r="G469" s="12" t="s">
-        <v>16</v>
+        <v>609</v>
       </c>
     </row>
     <row r="470" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A470" s="11" t="s">
-        <v>973</v>
+        <v>969</v>
       </c>
       <c r="B470" s="11">
         <v>6</v>
       </c>
       <c r="C470" s="12" t="s">
-        <v>972</v>
+        <v>968</v>
       </c>
       <c r="D470" s="12" t="s">
         <v>12</v>
@@ -18294,15 +18337,15 @@
       <c r="F470" s="12"/>
       <c r="G470" s="12"/>
     </row>
-    <row r="471" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="471" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A471" s="11" t="s">
-        <v>975</v>
+        <v>971</v>
       </c>
       <c r="B471" s="11">
         <v>6</v>
       </c>
       <c r="C471" s="12" t="s">
-        <v>974</v>
+        <v>970</v>
       </c>
       <c r="D471" s="12" t="s">
         <v>6</v>
@@ -18310,45 +18353,41 @@
       <c r="E471" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="F471" s="41" t="s">
-        <v>116</v>
+      <c r="F471" s="12" t="s">
+        <v>15</v>
       </c>
       <c r="G471" s="12" t="s">
-        <v>619</v>
-      </c>
-    </row>
-    <row r="472" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="472" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A472" s="11" t="s">
-        <v>977</v>
+        <v>973</v>
       </c>
       <c r="B472" s="11">
         <v>6</v>
       </c>
       <c r="C472" s="12" t="s">
-        <v>976</v>
+        <v>972</v>
       </c>
       <c r="D472" s="12" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E472" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="F472" s="12">
-        <v>1</v>
-      </c>
-      <c r="G472" s="12" t="s">
-        <v>58</v>
-      </c>
+        <v>612</v>
+      </c>
+      <c r="F472" s="12"/>
+      <c r="G472" s="12"/>
     </row>
     <row r="473" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A473" s="11" t="s">
-        <v>979</v>
+        <v>975</v>
       </c>
       <c r="B473" s="11">
         <v>6</v>
       </c>
       <c r="C473" s="12" t="s">
-        <v>978</v>
+        <v>974</v>
       </c>
       <c r="D473" s="12" t="s">
         <v>6</v>
@@ -18356,22 +18395,22 @@
       <c r="E473" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="F473" s="12">
-        <v>1</v>
+      <c r="F473" s="41" t="s">
+        <v>116</v>
       </c>
       <c r="G473" s="12" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="474" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="474" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A474" s="11" t="s">
-        <v>981</v>
+        <v>977</v>
       </c>
       <c r="B474" s="11">
         <v>6</v>
       </c>
       <c r="C474" s="12" t="s">
-        <v>980</v>
+        <v>976</v>
       </c>
       <c r="D474" s="12" t="s">
         <v>6</v>
@@ -18388,13 +18427,13 @@
     </row>
     <row r="475" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A475" s="11" t="s">
-        <v>983</v>
+        <v>979</v>
       </c>
       <c r="B475" s="11">
         <v>6</v>
       </c>
       <c r="C475" s="12" t="s">
-        <v>982</v>
+        <v>978</v>
       </c>
       <c r="D475" s="12" t="s">
         <v>6</v>
@@ -18411,78 +18450,82 @@
     </row>
     <row r="476" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A476" s="11" t="s">
+        <v>981</v>
+      </c>
+      <c r="B476" s="11">
+        <v>6</v>
+      </c>
+      <c r="C476" s="12" t="s">
+        <v>980</v>
+      </c>
+      <c r="D476" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="E476" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="F476" s="12">
+        <v>1</v>
+      </c>
+      <c r="G476" s="12" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="477" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A477" s="11" t="s">
+        <v>983</v>
+      </c>
+      <c r="B477" s="11">
+        <v>6</v>
+      </c>
+      <c r="C477" s="12" t="s">
+        <v>982</v>
+      </c>
+      <c r="D477" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="E477" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="F477" s="12">
+        <v>1</v>
+      </c>
+      <c r="G477" s="12" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="478" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A478" s="11" t="s">
         <v>985</v>
       </c>
-      <c r="B476" s="11">
-        <v>6</v>
-      </c>
-      <c r="C476" s="12" t="s">
+      <c r="B478" s="11">
+        <v>6</v>
+      </c>
+      <c r="C478" s="12" t="s">
         <v>984</v>
       </c>
-      <c r="D476" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="E476" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="F476" s="12">
-        <v>1</v>
-      </c>
-      <c r="G476" s="12" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="477" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A477" s="11" t="s">
-        <v>987</v>
-      </c>
-      <c r="B477" s="11">
-        <v>6</v>
-      </c>
-      <c r="C477" s="12" t="s">
-        <v>986</v>
-      </c>
-      <c r="D477" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="E477" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="F477" s="12">
-        <v>1</v>
-      </c>
-      <c r="G477" s="12" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="478" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A478" s="11" t="s">
-        <v>989</v>
-      </c>
-      <c r="B478" s="11">
-        <v>6</v>
-      </c>
-      <c r="C478" s="12" t="s">
-        <v>988</v>
-      </c>
       <c r="D478" s="12" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E478" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="F478" s="12"/>
-      <c r="G478" s="12"/>
+        <v>7</v>
+      </c>
+      <c r="F478" s="12">
+        <v>1</v>
+      </c>
+      <c r="G478" s="12" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="479" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A479" s="11" t="s">
-        <v>991</v>
+        <v>987</v>
       </c>
       <c r="B479" s="11">
         <v>6</v>
       </c>
       <c r="C479" s="12" t="s">
-        <v>990</v>
+        <v>986</v>
       </c>
       <c r="D479" s="12" t="s">
         <v>6</v>
@@ -18497,61 +18540,57 @@
         <v>58</v>
       </c>
     </row>
-    <row r="480" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="480" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A480" s="11" t="s">
-        <v>993</v>
+        <v>989</v>
       </c>
       <c r="B480" s="11">
         <v>6</v>
       </c>
       <c r="C480" s="12" t="s">
-        <v>992</v>
+        <v>988</v>
       </c>
       <c r="D480" s="12" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E480" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="F480" s="12">
-        <v>1</v>
-      </c>
-      <c r="G480" s="12" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="481" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A481" s="11" t="s">
-        <v>995</v>
+        <v>10</v>
+      </c>
+      <c r="F480" s="12"/>
+      <c r="G480" s="12"/>
+    </row>
+    <row r="481" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A481" s="43" t="s">
+        <v>1366</v>
       </c>
       <c r="B481" s="11">
         <v>6</v>
       </c>
-      <c r="C481" s="12" t="s">
-        <v>994</v>
-      </c>
-      <c r="D481" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="E481" s="12" t="s">
+      <c r="C481" s="42" t="s">
+        <v>1367</v>
+      </c>
+      <c r="D481" s="45" t="s">
+        <v>6</v>
+      </c>
+      <c r="E481" s="45" t="s">
         <v>7</v>
       </c>
       <c r="F481" s="12">
         <v>1</v>
       </c>
-      <c r="G481" s="12" t="s">
-        <v>58</v>
+      <c r="G481" s="45" t="s">
+        <v>1363</v>
       </c>
     </row>
     <row r="482" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A482" s="11" t="s">
-        <v>997</v>
+        <v>991</v>
       </c>
       <c r="B482" s="11">
         <v>6</v>
       </c>
       <c r="C482" s="12" t="s">
-        <v>996</v>
+        <v>990</v>
       </c>
       <c r="D482" s="12" t="s">
         <v>6</v>
@@ -18568,13 +18607,13 @@
     </row>
     <row r="483" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A483" s="11" t="s">
-        <v>999</v>
+        <v>993</v>
       </c>
       <c r="B483" s="11">
         <v>6</v>
       </c>
       <c r="C483" s="12" t="s">
-        <v>998</v>
+        <v>992</v>
       </c>
       <c r="D483" s="12" t="s">
         <v>6</v>
@@ -18591,13 +18630,13 @@
     </row>
     <row r="484" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A484" s="11" t="s">
-        <v>1001</v>
+        <v>995</v>
       </c>
       <c r="B484" s="11">
         <v>6</v>
       </c>
       <c r="C484" s="12" t="s">
-        <v>1000</v>
+        <v>994</v>
       </c>
       <c r="D484" s="12" t="s">
         <v>6</v>
@@ -18614,34 +18653,36 @@
     </row>
     <row r="485" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A485" s="11" t="s">
-        <v>1003</v>
+        <v>997</v>
       </c>
       <c r="B485" s="11">
         <v>6</v>
       </c>
       <c r="C485" s="12" t="s">
-        <v>1002</v>
+        <v>996</v>
       </c>
       <c r="D485" s="12" t="s">
         <v>6</v>
       </c>
       <c r="E485" s="12" t="s">
-        <v>474</v>
-      </c>
-      <c r="F485" s="12"/>
+        <v>7</v>
+      </c>
+      <c r="F485" s="12">
+        <v>1</v>
+      </c>
       <c r="G485" s="12" t="s">
-        <v>475</v>
+        <v>58</v>
       </c>
     </row>
     <row r="486" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A486" s="11" t="s">
-        <v>1005</v>
+        <v>999</v>
       </c>
       <c r="B486" s="11">
         <v>6</v>
       </c>
       <c r="C486" s="12" t="s">
-        <v>1004</v>
+        <v>998</v>
       </c>
       <c r="D486" s="12" t="s">
         <v>6</v>
@@ -18658,13 +18699,13 @@
     </row>
     <row r="487" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A487" s="11" t="s">
-        <v>1007</v>
+        <v>1001</v>
       </c>
       <c r="B487" s="11">
         <v>6</v>
       </c>
       <c r="C487" s="12" t="s">
-        <v>1006</v>
+        <v>1000</v>
       </c>
       <c r="D487" s="12" t="s">
         <v>6</v>
@@ -18681,36 +18722,34 @@
     </row>
     <row r="488" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A488" s="11" t="s">
-        <v>1009</v>
+        <v>1003</v>
       </c>
       <c r="B488" s="11">
         <v>6</v>
       </c>
       <c r="C488" s="12" t="s">
-        <v>1008</v>
+        <v>1002</v>
       </c>
       <c r="D488" s="12" t="s">
         <v>6</v>
       </c>
       <c r="E488" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="F488" s="12">
-        <v>1</v>
-      </c>
+        <v>474</v>
+      </c>
+      <c r="F488" s="12"/>
       <c r="G488" s="12" t="s">
-        <v>58</v>
+        <v>475</v>
       </c>
     </row>
     <row r="489" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A489" s="11" t="s">
-        <v>1011</v>
+        <v>1005</v>
       </c>
       <c r="B489" s="11">
         <v>6</v>
       </c>
       <c r="C489" s="12" t="s">
-        <v>1010</v>
+        <v>1004</v>
       </c>
       <c r="D489" s="12" t="s">
         <v>6</v>
@@ -18727,13 +18766,13 @@
     </row>
     <row r="490" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A490" s="11" t="s">
-        <v>1013</v>
+        <v>1007</v>
       </c>
       <c r="B490" s="11">
         <v>6</v>
       </c>
       <c r="C490" s="12" t="s">
-        <v>1012</v>
+        <v>1006</v>
       </c>
       <c r="D490" s="12" t="s">
         <v>6</v>
@@ -18750,13 +18789,13 @@
     </row>
     <row r="491" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A491" s="11" t="s">
-        <v>1015</v>
+        <v>1009</v>
       </c>
       <c r="B491" s="11">
         <v>6</v>
       </c>
       <c r="C491" s="12" t="s">
-        <v>1014</v>
+        <v>1008</v>
       </c>
       <c r="D491" s="12" t="s">
         <v>6</v>
@@ -18773,13 +18812,13 @@
     </row>
     <row r="492" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A492" s="11" t="s">
-        <v>1017</v>
+        <v>1011</v>
       </c>
       <c r="B492" s="11">
         <v>6</v>
       </c>
       <c r="C492" s="12" t="s">
-        <v>1016</v>
+        <v>1010</v>
       </c>
       <c r="D492" s="12" t="s">
         <v>6</v>
@@ -18796,84 +18835,153 @@
     </row>
     <row r="493" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A493" s="11" t="s">
+        <v>1013</v>
+      </c>
+      <c r="B493" s="11">
+        <v>6</v>
+      </c>
+      <c r="C493" s="12" t="s">
+        <v>1012</v>
+      </c>
+      <c r="D493" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="E493" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="F493" s="12">
+        <v>1</v>
+      </c>
+      <c r="G493" s="12" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="494" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A494" s="11" t="s">
+        <v>1015</v>
+      </c>
+      <c r="B494" s="11">
+        <v>6</v>
+      </c>
+      <c r="C494" s="12" t="s">
+        <v>1014</v>
+      </c>
+      <c r="D494" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="E494" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="F494" s="12">
+        <v>1</v>
+      </c>
+      <c r="G494" s="12" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="495" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A495" s="11" t="s">
+        <v>1017</v>
+      </c>
+      <c r="B495" s="11">
+        <v>6</v>
+      </c>
+      <c r="C495" s="12" t="s">
+        <v>1016</v>
+      </c>
+      <c r="D495" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="E495" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="F495" s="12">
+        <v>1</v>
+      </c>
+      <c r="G495" s="12" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="496" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A496" s="11" t="s">
         <v>1019</v>
       </c>
-      <c r="B493" s="11">
-        <v>6</v>
-      </c>
-      <c r="C493" s="12" t="s">
+      <c r="B496" s="11">
+        <v>6</v>
+      </c>
+      <c r="C496" s="12" t="s">
         <v>1018</v>
       </c>
-      <c r="D493" s="12" t="s">
+      <c r="D496" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="E493" s="12" t="s">
+      <c r="E496" s="12" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="494" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A494" s="11" t="s">
+    <row r="497" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A497" s="11" t="s">
         <v>1021</v>
       </c>
-      <c r="B494" s="11">
-        <v>6</v>
-      </c>
-      <c r="C494" s="12" t="s">
+      <c r="B497" s="11">
+        <v>6</v>
+      </c>
+      <c r="C497" s="12" t="s">
         <v>1020</v>
       </c>
-      <c r="D494" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="E494" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="F494" s="12">
-        <v>1</v>
-      </c>
-      <c r="G494" s="12" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="495" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A495" s="11" t="s">
+      <c r="D497" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="E497" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="F497" s="12">
+        <v>1</v>
+      </c>
+      <c r="G497" s="12" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="498" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A498" s="11" t="s">
         <v>1023</v>
       </c>
-      <c r="B495" s="11">
-        <v>6</v>
-      </c>
-      <c r="C495" s="12" t="s">
+      <c r="B498" s="11">
+        <v>6</v>
+      </c>
+      <c r="C498" s="12" t="s">
         <v>1022</v>
       </c>
-      <c r="D495" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="E495" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="F495" s="12">
-        <v>1</v>
-      </c>
-      <c r="G495" s="12" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="496" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A496" s="11" t="s">
+      <c r="D498" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="E498" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="F498" s="12">
+        <v>1</v>
+      </c>
+      <c r="G498" s="12" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="499" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A499" s="11" t="s">
         <v>1359</v>
       </c>
-      <c r="B496" s="11">
-        <v>6</v>
-      </c>
-      <c r="C496" s="11" t="s">
+      <c r="B499" s="11">
+        <v>6</v>
+      </c>
+      <c r="C499" s="11" t="s">
         <v>1354</v>
       </c>
-      <c r="E496" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="F496" s="11">
-        <v>1</v>
-      </c>
-      <c r="G496" s="11" t="s">
+      <c r="E499" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="F499" s="11">
+        <v>1</v>
+      </c>
+      <c r="G499" s="11" t="s">
         <v>1355</v>
       </c>
     </row>
